--- a/Versão5/ABNT/Ontologia_NBR15965_5I.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876CF01F-2EB8-432F-876D-03EB6F08C024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8820305D-A4F1-4440-9F36-799A2D0EE256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19847" uniqueCount="1798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19847" uniqueCount="1799">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -5454,12 +5454,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ - ]</t>
   </si>
   <si>
@@ -5475,16 +5469,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
     <t>[ IfcAnnotation ]</t>
   </si>
   <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
-    <t>[ IfcProperty ]</t>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
   </si>
 </sst>
 </file>
@@ -6094,7 +6097,39 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8576210E-162F-453B-B886-CD2163C7562E}"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -6592,14 +6627,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFEA285-1F1C-49D4-8690-0B8CB6A5C474}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -6610,7 +6645,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>19</v>
       </c>
@@ -6621,7 +6656,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
@@ -6632,7 +6667,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -6643,7 +6678,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
@@ -6655,7 +6690,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
@@ -6667,7 +6702,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
@@ -6678,7 +6713,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
@@ -6689,7 +6724,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
@@ -6700,7 +6735,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
@@ -6711,7 +6746,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>24</v>
       </c>
@@ -6722,7 +6757,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
@@ -6733,7 +6768,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -6744,7 +6779,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
@@ -6755,7 +6790,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
@@ -6766,7 +6801,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
@@ -6777,7 +6812,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>12</v>
       </c>
@@ -6788,19 +6823,19 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46244.492460069443</v>
+        <v>46249.319243749997</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>1540</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>1548</v>
       </c>
@@ -6811,7 +6846,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>1544</v>
       </c>
@@ -6823,7 +6858,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>1549</v>
       </c>
@@ -6835,7 +6870,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>18</v>
       </c>
@@ -6846,7 +6881,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>30</v>
       </c>
@@ -6857,7 +6892,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
@@ -6868,7 +6903,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
@@ -6879,7 +6914,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>1537</v>
       </c>
@@ -6890,7 +6925,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>1757</v>
       </c>
@@ -6901,7 +6936,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>1759</v>
       </c>
@@ -6912,7 +6947,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>1761</v>
       </c>
@@ -6923,7 +6958,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>1763</v>
       </c>
@@ -6934,7 +6969,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>1765</v>
       </c>
@@ -6945,7 +6980,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>1767</v>
       </c>
@@ -6956,7 +6991,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>1769</v>
       </c>
@@ -6967,7 +7002,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>1771</v>
       </c>
@@ -6978,7 +7013,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>1773</v>
       </c>
@@ -6989,7 +7024,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>1775</v>
       </c>
@@ -7000,7 +7035,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>1777</v>
       </c>
@@ -7011,7 +7046,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>1779</v>
       </c>
@@ -7022,7 +7057,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="76" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="76" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>1781</v>
       </c>
@@ -7049,34 +7084,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A90C8D-F4F0-474F-8F2D-D62CBC6EB14C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA36"/>
-  <sheetFormatPr defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" style="65" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" style="32" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="32" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" style="32" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="12.296875" style="32" customWidth="1"/>
+    <col min="6" max="6" width="15.69921875" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.69921875" style="32" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="75.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.1640625" customWidth="1"/>
+    <col min="14" max="14" width="10.796875" customWidth="1"/>
+    <col min="15" max="15" width="15.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="75.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.19921875" customWidth="1"/>
     <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="9.1640625" customWidth="1"/>
+    <col min="20" max="20" width="9.19921875" customWidth="1"/>
     <col min="21" max="21" width="10" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="44" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.69921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="35.796875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11" customWidth="1"/>
-    <col min="27" max="27" width="64.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="64.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="25.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="25.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>1482</v>
       </c>
@@ -7159,7 +7194,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -7238,10 +7273,10 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="42" t="s">
-        <v>1787</v>
+        <v>1794</v>
       </c>
       <c r="Y2" s="42" t="s">
-        <v>1788</v>
+        <v>1795</v>
       </c>
       <c r="Z2" s="42" t="s">
         <v>1552</v>
@@ -7250,7 +7285,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -7329,7 +7364,7 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="42" t="s">
-        <v>1789</v>
+        <v>1796</v>
       </c>
       <c r="Y3" s="42" t="s">
         <v>1797</v>
@@ -7341,7 +7376,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -7420,10 +7455,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Y4" s="42" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="Z4" s="42" t="s">
         <v>1554</v>
@@ -7432,7 +7467,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -7511,10 +7546,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="42" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="Y5" s="42" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="Z5" s="42" t="s">
         <v>1555</v>
@@ -7523,7 +7558,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -7602,10 +7637,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Y6" s="42" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="Z6" s="42" t="s">
         <v>1556</v>
@@ -7614,7 +7649,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -7693,10 +7728,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Y7" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Z7" s="42" t="s">
         <v>1557</v>
@@ -7705,7 +7740,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -7784,10 +7819,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Y8" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Z8" s="42" t="s">
         <v>1558</v>
@@ -7796,7 +7831,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -7875,10 +7910,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Y9" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Z9" s="42" t="s">
         <v>1559</v>
@@ -7887,7 +7922,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -7966,10 +8001,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Y10" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Z10" s="42" t="s">
         <v>1560</v>
@@ -7978,7 +8013,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -8057,10 +8092,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Y11" s="42" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="Z11" s="42" t="s">
         <v>1561</v>
@@ -8069,7 +8104,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -8148,10 +8183,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="42" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="Y12" s="42" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
       <c r="Z12" s="42" t="s">
         <v>1562</v>
@@ -8160,7 +8195,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -8239,10 +8274,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="42" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="Y13" s="42" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
       <c r="Z13" s="42" t="s">
         <v>1563</v>
@@ -8251,7 +8286,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -8330,10 +8365,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y14" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z14" s="42" t="s">
         <v>1475</v>
@@ -8342,7 +8377,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -8421,10 +8456,10 @@
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y15" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z15" s="63" t="s">
         <v>1628</v>
@@ -8433,7 +8468,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -8512,10 +8547,10 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y16" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z16" s="63" t="s">
         <v>1629</v>
@@ -8524,7 +8559,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -8603,10 +8638,10 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y17" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z17" s="63" t="s">
         <v>1630</v>
@@ -8615,7 +8650,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -8694,10 +8729,10 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y18" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z18" s="63" t="s">
         <v>1631</v>
@@ -8706,7 +8741,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -8785,10 +8820,10 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y19" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z19" s="63" t="s">
         <v>1632</v>
@@ -8797,7 +8832,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -8876,10 +8911,10 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y20" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z20" s="63" t="s">
         <v>1633</v>
@@ -8888,7 +8923,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -8967,10 +9002,10 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y21" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z21" s="63" t="s">
         <v>1634</v>
@@ -8979,7 +9014,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -9058,10 +9093,10 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y22" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z22" s="63" t="s">
         <v>1635</v>
@@ -9070,7 +9105,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -9149,10 +9184,10 @@
         <v>Key-ABNT-23</v>
       </c>
       <c r="X23" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y23" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z23" s="63" t="s">
         <v>1636</v>
@@ -9161,7 +9196,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -9240,10 +9275,10 @@
         <v>Key-ABNT-24</v>
       </c>
       <c r="X24" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y24" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z24" s="63" t="s">
         <v>1637</v>
@@ -9252,7 +9287,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -9331,10 +9366,10 @@
         <v>Key-ABNT-25</v>
       </c>
       <c r="X25" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y25" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z25" s="63" t="s">
         <v>1638</v>
@@ -9343,7 +9378,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -9422,10 +9457,10 @@
         <v>Key-ABNT-26</v>
       </c>
       <c r="X26" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y26" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z26" s="63" t="s">
         <v>1639</v>
@@ -9434,7 +9469,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -9513,10 +9548,10 @@
         <v>Key-ABNT-27</v>
       </c>
       <c r="X27" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y27" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z27" s="63" t="s">
         <v>1640</v>
@@ -9525,7 +9560,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -9604,10 +9639,10 @@
         <v>Key-ABNT-28</v>
       </c>
       <c r="X28" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y28" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z28" s="63" t="s">
         <v>1641</v>
@@ -9616,7 +9651,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -9695,10 +9730,10 @@
         <v>Key-ABNT-29</v>
       </c>
       <c r="X29" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y29" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z29" s="63" t="s">
         <v>1642</v>
@@ -9707,7 +9742,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -9786,10 +9821,10 @@
         <v>Key-ABNT-30</v>
       </c>
       <c r="X30" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y30" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z30" s="63" t="s">
         <v>1643</v>
@@ -9798,7 +9833,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="56">
         <v>31</v>
       </c>
@@ -9877,10 +9912,10 @@
         <v>Key-ABNT-31</v>
       </c>
       <c r="X31" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y31" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z31" s="63" t="s">
         <v>1644</v>
@@ -9889,7 +9924,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="56">
         <v>32</v>
       </c>
@@ -9968,10 +10003,10 @@
         <v>Key-ABNT-32</v>
       </c>
       <c r="X32" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y32" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z32" s="63" t="s">
         <v>1645</v>
@@ -9980,7 +10015,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="56">
         <v>33</v>
       </c>
@@ -10059,10 +10094,10 @@
         <v>Key-ABNT-33</v>
       </c>
       <c r="X33" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y33" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z33" s="63" t="s">
         <v>1646</v>
@@ -10071,7 +10106,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="56">
         <v>34</v>
       </c>
@@ -10150,10 +10185,10 @@
         <v>Key-ABNT-34</v>
       </c>
       <c r="X34" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y34" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z34" s="63" t="s">
         <v>1647</v>
@@ -10162,7 +10197,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="56">
         <v>35</v>
       </c>
@@ -10241,10 +10276,10 @@
         <v>Key-ABNT-35</v>
       </c>
       <c r="X35" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y35" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z35" s="63" t="s">
         <v>1648</v>
@@ -10253,7 +10288,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="56">
         <v>36</v>
       </c>
@@ -10332,10 +10367,10 @@
         <v>Key-ABNT-36</v>
       </c>
       <c r="X36" s="77" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Y36" s="78" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Z36" s="63" t="s">
         <v>1649</v>
@@ -10345,17 +10380,29 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
+  <conditionalFormatting sqref="Z15:Z36">
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+  <conditionalFormatting sqref="AA1 A15:B36">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z15:Z36">
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
+  <conditionalFormatting sqref="F2:F14">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA14 A2:B36">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="AA2:AA14 A2:B14">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10370,13 +10417,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1AA270-C700-44D7-AFAB-8480CF5F2B6E}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>1483</v>
       </c>
@@ -10441,7 +10488,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -10508,7 +10555,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10523,14 +10570,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBE7ADA-121D-48D5-88A4-2E192550983E}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.69921875" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -10541,7 +10588,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -10554,7 +10601,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10566,39 +10613,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AA732"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.296875" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.83203125" style="9" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.83203125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.796875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.796875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="16.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.296875" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23.5" style="9" customWidth="1"/>
     <col min="14" max="14" width="6" style="9" customWidth="1"/>
-    <col min="15" max="15" width="45.6640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="45.69921875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.69921875" style="1" customWidth="1"/>
     <col min="17" max="17" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.83203125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.83203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="14.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.796875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="22.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.796875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="14.69921875" style="1" customWidth="1"/>
     <col min="26" max="26" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.1640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="11.19921875" style="1" customWidth="1"/>
     <col min="28" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>31</v>
       </c>
@@ -10681,7 +10728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -10764,7 +10811,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -10847,7 +10894,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -10930,7 +10977,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>5</v>
       </c>
@@ -11013,7 +11060,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>6</v>
       </c>
@@ -11096,7 +11143,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>7</v>
       </c>
@@ -11179,7 +11226,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>8</v>
       </c>
@@ -11262,7 +11309,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>9</v>
       </c>
@@ -11345,7 +11392,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>10</v>
       </c>
@@ -11428,7 +11475,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>11</v>
       </c>
@@ -11511,7 +11558,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>12</v>
       </c>
@@ -11594,7 +11641,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>13</v>
       </c>
@@ -11677,7 +11724,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>14</v>
       </c>
@@ -11760,7 +11807,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>15</v>
       </c>
@@ -11843,7 +11890,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>16</v>
       </c>
@@ -11926,7 +11973,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>17</v>
       </c>
@@ -12009,7 +12056,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>18</v>
       </c>
@@ -12092,7 +12139,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>19</v>
       </c>
@@ -12175,7 +12222,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>20</v>
       </c>
@@ -12258,7 +12305,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>21</v>
       </c>
@@ -12341,7 +12388,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>22</v>
       </c>
@@ -12424,7 +12471,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>23</v>
       </c>
@@ -12507,7 +12554,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>24</v>
       </c>
@@ -12590,7 +12637,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>25</v>
       </c>
@@ -12673,7 +12720,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>26</v>
       </c>
@@ -12756,7 +12803,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>27</v>
       </c>
@@ -12839,7 +12886,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>28</v>
       </c>
@@ -12922,7 +12969,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>29</v>
       </c>
@@ -13005,7 +13052,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>30</v>
       </c>
@@ -13088,7 +13135,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>31</v>
       </c>
@@ -13171,7 +13218,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>32</v>
       </c>
@@ -13254,7 +13301,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>33</v>
       </c>
@@ -13337,7 +13384,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>34</v>
       </c>
@@ -13420,7 +13467,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
         <v>35</v>
       </c>
@@ -13503,7 +13550,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
         <v>36</v>
       </c>
@@ -13586,7 +13633,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
         <v>37</v>
       </c>
@@ -13669,7 +13716,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
         <v>38</v>
       </c>
@@ -13752,7 +13799,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>39</v>
       </c>
@@ -13835,7 +13882,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <v>40</v>
       </c>
@@ -13918,7 +13965,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <v>41</v>
       </c>
@@ -14001,7 +14048,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <v>42</v>
       </c>
@@ -14084,7 +14131,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <v>43</v>
       </c>
@@ -14167,7 +14214,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <v>44</v>
       </c>
@@ -14250,7 +14297,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <v>45</v>
       </c>
@@ -14333,7 +14380,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <v>46</v>
       </c>
@@ -14416,7 +14463,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <v>47</v>
       </c>
@@ -14499,7 +14546,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <v>48</v>
       </c>
@@ -14582,7 +14629,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <v>49</v>
       </c>
@@ -14665,7 +14712,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <v>50</v>
       </c>
@@ -14748,7 +14795,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <v>51</v>
       </c>
@@ -14831,7 +14878,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <v>52</v>
       </c>
@@ -14914,7 +14961,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <v>53</v>
       </c>
@@ -14997,7 +15044,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
         <v>54</v>
       </c>
@@ -15080,7 +15127,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <v>55</v>
       </c>
@@ -15163,7 +15210,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <v>56</v>
       </c>
@@ -15246,7 +15293,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <v>57</v>
       </c>
@@ -15329,7 +15376,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <v>58</v>
       </c>
@@ -15412,7 +15459,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
         <v>59</v>
       </c>
@@ -15495,7 +15542,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12">
         <v>60</v>
       </c>
@@ -15578,7 +15625,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
         <v>61</v>
       </c>
@@ -15661,7 +15708,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <v>62</v>
       </c>
@@ -15744,7 +15791,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <v>63</v>
       </c>
@@ -15827,7 +15874,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <v>64</v>
       </c>
@@ -15910,7 +15957,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
         <v>65</v>
       </c>
@@ -15993,7 +16040,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12">
         <v>66</v>
       </c>
@@ -16076,7 +16123,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12">
         <v>67</v>
       </c>
@@ -16159,7 +16206,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12">
         <v>68</v>
       </c>
@@ -16242,7 +16289,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <v>69</v>
       </c>
@@ -16325,7 +16372,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <v>70</v>
       </c>
@@ -16408,7 +16455,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <v>71</v>
       </c>
@@ -16491,7 +16538,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12">
         <v>72</v>
       </c>
@@ -16574,7 +16621,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
         <v>73</v>
       </c>
@@ -16657,7 +16704,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
         <v>74</v>
       </c>
@@ -16740,7 +16787,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12">
         <v>75</v>
       </c>
@@ -16823,7 +16870,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
         <v>76</v>
       </c>
@@ -16906,7 +16953,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
         <v>77</v>
       </c>
@@ -16989,7 +17036,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
         <v>78</v>
       </c>
@@ -17072,7 +17119,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12">
         <v>79</v>
       </c>
@@ -17155,7 +17202,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
         <v>80</v>
       </c>
@@ -17238,7 +17285,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
         <v>81</v>
       </c>
@@ -17321,7 +17368,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
         <v>82</v>
       </c>
@@ -17404,7 +17451,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12">
         <v>83</v>
       </c>
@@ -17487,7 +17534,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12">
         <v>84</v>
       </c>
@@ -17570,7 +17617,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12">
         <v>85</v>
       </c>
@@ -17653,7 +17700,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
         <v>86</v>
       </c>
@@ -17736,7 +17783,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12">
         <v>87</v>
       </c>
@@ -17819,7 +17866,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12">
         <v>88</v>
       </c>
@@ -17902,7 +17949,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12">
         <v>89</v>
       </c>
@@ -17985,7 +18032,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12">
         <v>90</v>
       </c>
@@ -18068,7 +18115,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12">
         <v>91</v>
       </c>
@@ -18151,7 +18198,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12">
         <v>92</v>
       </c>
@@ -18234,7 +18281,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12">
         <v>93</v>
       </c>
@@ -18317,7 +18364,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12">
         <v>94</v>
       </c>
@@ -18400,7 +18447,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12">
         <v>95</v>
       </c>
@@ -18483,7 +18530,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12">
         <v>96</v>
       </c>
@@ -18566,7 +18613,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12">
         <v>97</v>
       </c>
@@ -18649,7 +18696,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12">
         <v>98</v>
       </c>
@@ -18732,7 +18779,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12">
         <v>99</v>
       </c>
@@ -18815,7 +18862,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12">
         <v>100</v>
       </c>
@@ -18898,7 +18945,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12">
         <v>101</v>
       </c>
@@ -18981,7 +19028,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12">
         <v>102</v>
       </c>
@@ -19064,7 +19111,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="12">
         <v>103</v>
       </c>
@@ -19147,7 +19194,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12">
         <v>104</v>
       </c>
@@ -19230,7 +19277,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="12">
         <v>105</v>
       </c>
@@ -19313,7 +19360,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12">
         <v>106</v>
       </c>
@@ -19396,7 +19443,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="12">
         <v>107</v>
       </c>
@@ -19479,7 +19526,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12">
         <v>108</v>
       </c>
@@ -19562,7 +19609,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="12">
         <v>109</v>
       </c>
@@ -19645,7 +19692,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12">
         <v>110</v>
       </c>
@@ -19728,7 +19775,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12">
         <v>111</v>
       </c>
@@ -19811,7 +19858,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12">
         <v>112</v>
       </c>
@@ -19894,7 +19941,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="12">
         <v>113</v>
       </c>
@@ -19977,7 +20024,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12">
         <v>114</v>
       </c>
@@ -20060,7 +20107,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="12">
         <v>115</v>
       </c>
@@ -20143,7 +20190,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12">
         <v>116</v>
       </c>
@@ -20226,7 +20273,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="12">
         <v>117</v>
       </c>
@@ -20309,7 +20356,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12">
         <v>118</v>
       </c>
@@ -20392,7 +20439,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="12">
         <v>119</v>
       </c>
@@ -20475,7 +20522,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12">
         <v>120</v>
       </c>
@@ -20558,7 +20605,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="12">
         <v>121</v>
       </c>
@@ -20641,7 +20688,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12">
         <v>122</v>
       </c>
@@ -20724,7 +20771,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="12">
         <v>123</v>
       </c>
@@ -20807,7 +20854,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12">
         <v>124</v>
       </c>
@@ -20890,7 +20937,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12">
         <v>125</v>
       </c>
@@ -20973,7 +21020,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12">
         <v>126</v>
       </c>
@@ -21056,7 +21103,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12">
         <v>127</v>
       </c>
@@ -21139,7 +21186,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12">
         <v>128</v>
       </c>
@@ -21222,7 +21269,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="12">
         <v>129</v>
       </c>
@@ -21305,7 +21352,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12">
         <v>130</v>
       </c>
@@ -21388,7 +21435,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12">
         <v>131</v>
       </c>
@@ -21471,7 +21518,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12">
         <v>132</v>
       </c>
@@ -21554,7 +21601,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12">
         <v>133</v>
       </c>
@@ -21637,7 +21684,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12">
         <v>134</v>
       </c>
@@ -21720,7 +21767,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="12">
         <v>135</v>
       </c>
@@ -21803,7 +21850,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12">
         <v>136</v>
       </c>
@@ -21886,7 +21933,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12">
         <v>137</v>
       </c>
@@ -21969,7 +22016,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12">
         <v>138</v>
       </c>
@@ -22052,7 +22099,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12">
         <v>139</v>
       </c>
@@ -22135,7 +22182,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12">
         <v>140</v>
       </c>
@@ -22218,7 +22265,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12">
         <v>141</v>
       </c>
@@ -22301,7 +22348,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12">
         <v>142</v>
       </c>
@@ -22384,7 +22431,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12">
         <v>143</v>
       </c>
@@ -22467,7 +22514,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12">
         <v>144</v>
       </c>
@@ -22550,7 +22597,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12">
         <v>145</v>
       </c>
@@ -22633,7 +22680,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12">
         <v>146</v>
       </c>
@@ -22716,7 +22763,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12">
         <v>147</v>
       </c>
@@ -22799,7 +22846,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12">
         <v>148</v>
       </c>
@@ -22882,7 +22929,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12">
         <v>149</v>
       </c>
@@ -22965,7 +23012,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12">
         <v>150</v>
       </c>
@@ -23048,7 +23095,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12">
         <v>151</v>
       </c>
@@ -23131,7 +23178,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12">
         <v>152</v>
       </c>
@@ -23214,7 +23261,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12">
         <v>153</v>
       </c>
@@ -23297,7 +23344,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12">
         <v>154</v>
       </c>
@@ -23380,7 +23427,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12">
         <v>155</v>
       </c>
@@ -23463,7 +23510,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12">
         <v>156</v>
       </c>
@@ -23546,7 +23593,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="12">
         <v>157</v>
       </c>
@@ -23629,7 +23676,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12">
         <v>158</v>
       </c>
@@ -23712,7 +23759,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12">
         <v>159</v>
       </c>
@@ -23795,7 +23842,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12">
         <v>160</v>
       </c>
@@ -23878,7 +23925,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12">
         <v>161</v>
       </c>
@@ -23961,7 +24008,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12">
         <v>162</v>
       </c>
@@ -24044,7 +24091,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12">
         <v>163</v>
       </c>
@@ -24127,7 +24174,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12">
         <v>164</v>
       </c>
@@ -24210,7 +24257,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="165" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="12">
         <v>165</v>
       </c>
@@ -24293,7 +24340,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12">
         <v>166</v>
       </c>
@@ -24376,7 +24423,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="12">
         <v>167</v>
       </c>
@@ -24459,7 +24506,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="168" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12">
         <v>168</v>
       </c>
@@ -24542,7 +24589,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12">
         <v>169</v>
       </c>
@@ -24625,7 +24672,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="170" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12">
         <v>170</v>
       </c>
@@ -24708,7 +24755,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="12">
         <v>171</v>
       </c>
@@ -24791,7 +24838,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="172" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12">
         <v>172</v>
       </c>
@@ -24874,7 +24921,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="12">
         <v>173</v>
       </c>
@@ -24957,7 +25004,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12">
         <v>174</v>
       </c>
@@ -25040,7 +25087,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="175" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12">
         <v>175</v>
       </c>
@@ -25123,7 +25170,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12">
         <v>176</v>
       </c>
@@ -25206,7 +25253,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="12">
         <v>177</v>
       </c>
@@ -25289,7 +25336,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12">
         <v>178</v>
       </c>
@@ -25372,7 +25419,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="12">
         <v>179</v>
       </c>
@@ -25455,7 +25502,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12">
         <v>180</v>
       </c>
@@ -25538,7 +25585,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="12">
         <v>181</v>
       </c>
@@ -25621,7 +25668,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12">
         <v>182</v>
       </c>
@@ -25704,7 +25751,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12">
         <v>183</v>
       </c>
@@ -25787,7 +25834,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="184" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12">
         <v>184</v>
       </c>
@@ -25870,7 +25917,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="185" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="12">
         <v>185</v>
       </c>
@@ -25953,7 +26000,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12">
         <v>186</v>
       </c>
@@ -26036,7 +26083,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="12">
         <v>187</v>
       </c>
@@ -26119,7 +26166,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12">
         <v>188</v>
       </c>
@@ -26202,7 +26249,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="189" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12">
         <v>189</v>
       </c>
@@ -26285,7 +26332,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12">
         <v>190</v>
       </c>
@@ -26368,7 +26415,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="12">
         <v>191</v>
       </c>
@@ -26451,7 +26498,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="192" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12">
         <v>192</v>
       </c>
@@ -26534,7 +26581,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="193" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12">
         <v>193</v>
       </c>
@@ -26617,7 +26664,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12">
         <v>194</v>
       </c>
@@ -26700,7 +26747,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="12">
         <v>195</v>
       </c>
@@ -26783,7 +26830,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12">
         <v>196</v>
       </c>
@@ -26866,7 +26913,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="197" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="12">
         <v>197</v>
       </c>
@@ -26949,7 +26996,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="198" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12">
         <v>198</v>
       </c>
@@ -27032,7 +27079,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="199" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="12">
         <v>199</v>
       </c>
@@ -27115,7 +27162,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="200" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12">
         <v>200</v>
       </c>
@@ -27198,7 +27245,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="12">
         <v>201</v>
       </c>
@@ -27281,7 +27328,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="202" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12">
         <v>202</v>
       </c>
@@ -27364,7 +27411,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="12">
         <v>203</v>
       </c>
@@ -27447,7 +27494,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="204" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12">
         <v>204</v>
       </c>
@@ -27530,7 +27577,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="205" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="12">
         <v>205</v>
       </c>
@@ -27613,7 +27660,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="206" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12">
         <v>206</v>
       </c>
@@ -27696,7 +27743,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="12">
         <v>207</v>
       </c>
@@ -27779,7 +27826,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12">
         <v>208</v>
       </c>
@@ -27862,7 +27909,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="209" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="12">
         <v>209</v>
       </c>
@@ -27945,7 +27992,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="210" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12">
         <v>210</v>
       </c>
@@ -28028,7 +28075,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="12">
         <v>211</v>
       </c>
@@ -28111,7 +28158,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="212" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12">
         <v>212</v>
       </c>
@@ -28194,7 +28241,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="213" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="12">
         <v>213</v>
       </c>
@@ -28277,7 +28324,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="214" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12">
         <v>214</v>
       </c>
@@ -28360,7 +28407,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="215" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="12">
         <v>215</v>
       </c>
@@ -28443,7 +28490,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="216" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12">
         <v>216</v>
       </c>
@@ -28526,7 +28573,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="217" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="12">
         <v>217</v>
       </c>
@@ -28609,7 +28656,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="218" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12">
         <v>218</v>
       </c>
@@ -28692,7 +28739,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="219" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="12">
         <v>219</v>
       </c>
@@ -28775,7 +28822,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="220" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12">
         <v>220</v>
       </c>
@@ -28858,7 +28905,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="221" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="12">
         <v>221</v>
       </c>
@@ -28941,7 +28988,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="222" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12">
         <v>222</v>
       </c>
@@ -29024,7 +29071,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="223" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="12">
         <v>223</v>
       </c>
@@ -29107,7 +29154,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="224" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12">
         <v>224</v>
       </c>
@@ -29190,7 +29237,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="225" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="12">
         <v>225</v>
       </c>
@@ -29273,7 +29320,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="226" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12">
         <v>226</v>
       </c>
@@ -29356,7 +29403,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="227" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="12">
         <v>227</v>
       </c>
@@ -29439,7 +29486,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="228" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12">
         <v>228</v>
       </c>
@@ -29522,7 +29569,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="229" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="12">
         <v>229</v>
       </c>
@@ -29605,7 +29652,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="230" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12">
         <v>230</v>
       </c>
@@ -29688,7 +29735,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="231" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="12">
         <v>231</v>
       </c>
@@ -29771,7 +29818,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="232" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12">
         <v>232</v>
       </c>
@@ -29854,7 +29901,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="233" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="12">
         <v>233</v>
       </c>
@@ -29937,7 +29984,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="234" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12">
         <v>234</v>
       </c>
@@ -30020,7 +30067,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="235" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="12">
         <v>235</v>
       </c>
@@ -30103,7 +30150,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="236" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12">
         <v>236</v>
       </c>
@@ -30186,7 +30233,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="237" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="12">
         <v>237</v>
       </c>
@@ -30269,7 +30316,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="238" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12">
         <v>238</v>
       </c>
@@ -30352,7 +30399,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="239" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="12">
         <v>239</v>
       </c>
@@ -30435,7 +30482,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="240" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12">
         <v>240</v>
       </c>
@@ -30518,7 +30565,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="241" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="12">
         <v>241</v>
       </c>
@@ -30601,7 +30648,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="242" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12">
         <v>242</v>
       </c>
@@ -30684,7 +30731,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="243" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="12">
         <v>243</v>
       </c>
@@ -30767,7 +30814,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="244" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12">
         <v>244</v>
       </c>
@@ -30850,7 +30897,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="245" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="12">
         <v>245</v>
       </c>
@@ -30933,7 +30980,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="246" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12">
         <v>246</v>
       </c>
@@ -31016,7 +31063,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="247" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="12">
         <v>247</v>
       </c>
@@ -31099,7 +31146,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="248" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12">
         <v>248</v>
       </c>
@@ -31182,7 +31229,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="249" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="12">
         <v>249</v>
       </c>
@@ -31265,7 +31312,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="250" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12">
         <v>250</v>
       </c>
@@ -31348,7 +31395,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="251" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="12">
         <v>251</v>
       </c>
@@ -31431,7 +31478,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="252" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12">
         <v>252</v>
       </c>
@@ -31514,7 +31561,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="253" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="12">
         <v>253</v>
       </c>
@@ -31597,7 +31644,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="254" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12">
         <v>254</v>
       </c>
@@ -31680,7 +31727,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="255" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="12">
         <v>255</v>
       </c>
@@ -31763,7 +31810,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="256" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12">
         <v>256</v>
       </c>
@@ -31846,7 +31893,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="257" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="12">
         <v>257</v>
       </c>
@@ -31929,7 +31976,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="258" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12">
         <v>258</v>
       </c>
@@ -32012,7 +32059,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="259" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="12">
         <v>259</v>
       </c>
@@ -32095,7 +32142,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="260" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12">
         <v>260</v>
       </c>
@@ -32178,7 +32225,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="261" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="12">
         <v>261</v>
       </c>
@@ -32261,7 +32308,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="262" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12">
         <v>262</v>
       </c>
@@ -32344,7 +32391,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="263" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12">
         <v>263</v>
       </c>
@@ -32427,7 +32474,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="264" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12">
         <v>264</v>
       </c>
@@ -32510,7 +32557,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="265" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12">
         <v>265</v>
       </c>
@@ -32593,7 +32640,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="266" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12">
         <v>266</v>
       </c>
@@ -32676,7 +32723,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="267" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12">
         <v>267</v>
       </c>
@@ -32759,7 +32806,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="268" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12">
         <v>268</v>
       </c>
@@ -32842,7 +32889,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="269" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="12">
         <v>269</v>
       </c>
@@ -32925,7 +32972,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="270" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12">
         <v>270</v>
       </c>
@@ -33008,7 +33055,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="271" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="12">
         <v>271</v>
       </c>
@@ -33091,7 +33138,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="272" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12">
         <v>272</v>
       </c>
@@ -33174,7 +33221,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="273" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="12">
         <v>273</v>
       </c>
@@ -33257,7 +33304,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="274" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12">
         <v>274</v>
       </c>
@@ -33340,7 +33387,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="275" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="12">
         <v>275</v>
       </c>
@@ -33423,7 +33470,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="276" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12">
         <v>276</v>
       </c>
@@ -33506,7 +33553,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="277" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="12">
         <v>277</v>
       </c>
@@ -33589,7 +33636,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="278" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12">
         <v>278</v>
       </c>
@@ -33672,7 +33719,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="279" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="12">
         <v>279</v>
       </c>
@@ -33755,7 +33802,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="280" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12">
         <v>280</v>
       </c>
@@ -33838,7 +33885,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="281" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="12">
         <v>281</v>
       </c>
@@ -33921,7 +33968,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="282" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12">
         <v>282</v>
       </c>
@@ -34004,7 +34051,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="283" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="12">
         <v>283</v>
       </c>
@@ -34087,7 +34134,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="284" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12">
         <v>284</v>
       </c>
@@ -34170,7 +34217,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="285" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="12">
         <v>285</v>
       </c>
@@ -34253,7 +34300,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="286" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12">
         <v>286</v>
       </c>
@@ -34336,7 +34383,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="287" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="12">
         <v>287</v>
       </c>
@@ -34419,7 +34466,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="288" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12">
         <v>288</v>
       </c>
@@ -34502,7 +34549,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="289" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="12">
         <v>289</v>
       </c>
@@ -34585,7 +34632,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="290" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12">
         <v>290</v>
       </c>
@@ -34668,7 +34715,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="291" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="12">
         <v>291</v>
       </c>
@@ -34751,7 +34798,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="292" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12">
         <v>292</v>
       </c>
@@ -34834,7 +34881,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="293" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="12">
         <v>293</v>
       </c>
@@ -34917,7 +34964,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="294" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12">
         <v>294</v>
       </c>
@@ -35000,7 +35047,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="295" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="12">
         <v>295</v>
       </c>
@@ -35083,7 +35130,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="296" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12">
         <v>296</v>
       </c>
@@ -35166,7 +35213,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="297" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="12">
         <v>297</v>
       </c>
@@ -35249,7 +35296,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="298" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12">
         <v>298</v>
       </c>
@@ -35332,7 +35379,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="299" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="12">
         <v>299</v>
       </c>
@@ -35415,7 +35462,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="300" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12">
         <v>300</v>
       </c>
@@ -35498,7 +35545,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="301" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="12">
         <v>301</v>
       </c>
@@ -35581,7 +35628,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="302" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="12">
         <v>302</v>
       </c>
@@ -35664,7 +35711,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="303" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="12">
         <v>303</v>
       </c>
@@ -35747,7 +35794,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="304" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="12">
         <v>304</v>
       </c>
@@ -35830,7 +35877,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="305" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="12">
         <v>305</v>
       </c>
@@ -35913,7 +35960,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="306" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="12">
         <v>306</v>
       </c>
@@ -35996,7 +36043,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="307" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="12">
         <v>307</v>
       </c>
@@ -36079,7 +36126,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="308" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="12">
         <v>308</v>
       </c>
@@ -36162,7 +36209,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="309" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="12">
         <v>309</v>
       </c>
@@ -36245,7 +36292,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="310" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="12">
         <v>310</v>
       </c>
@@ -36328,7 +36375,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="311" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="12">
         <v>311</v>
       </c>
@@ -36411,7 +36458,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="312" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="12">
         <v>312</v>
       </c>
@@ -36494,7 +36541,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="313" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="12">
         <v>313</v>
       </c>
@@ -36577,7 +36624,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="314" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="12">
         <v>314</v>
       </c>
@@ -36660,7 +36707,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="315" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="12">
         <v>315</v>
       </c>
@@ -36743,7 +36790,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="316" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="12">
         <v>316</v>
       </c>
@@ -36826,7 +36873,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="317" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="12">
         <v>317</v>
       </c>
@@ -36909,7 +36956,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="318" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="12">
         <v>318</v>
       </c>
@@ -36992,7 +37039,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="319" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="12">
         <v>319</v>
       </c>
@@ -37075,7 +37122,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="320" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="12">
         <v>320</v>
       </c>
@@ -37158,7 +37205,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="321" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="12">
         <v>321</v>
       </c>
@@ -37241,7 +37288,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="322" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="12">
         <v>322</v>
       </c>
@@ -37324,7 +37371,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="323" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="12">
         <v>323</v>
       </c>
@@ -37407,7 +37454,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="324" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="12">
         <v>324</v>
       </c>
@@ -37490,7 +37537,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="325" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="12">
         <v>325</v>
       </c>
@@ -37573,7 +37620,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="326" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="12">
         <v>326</v>
       </c>
@@ -37656,7 +37703,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="327" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="12">
         <v>327</v>
       </c>
@@ -37739,7 +37786,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="328" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="12">
         <v>328</v>
       </c>
@@ -37822,7 +37869,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="329" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="12">
         <v>329</v>
       </c>
@@ -37905,7 +37952,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="330" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="12">
         <v>330</v>
       </c>
@@ -37988,7 +38035,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="331" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="12">
         <v>331</v>
       </c>
@@ -38071,7 +38118,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="332" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="12">
         <v>332</v>
       </c>
@@ -38154,7 +38201,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="333" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="12">
         <v>333</v>
       </c>
@@ -38237,7 +38284,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="334" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="12">
         <v>334</v>
       </c>
@@ -38320,7 +38367,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="335" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="12">
         <v>335</v>
       </c>
@@ -38403,7 +38450,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="336" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="12">
         <v>336</v>
       </c>
@@ -38486,7 +38533,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="337" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="12">
         <v>337</v>
       </c>
@@ -38569,7 +38616,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="338" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="12">
         <v>338</v>
       </c>
@@ -38652,7 +38699,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="339" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="12">
         <v>339</v>
       </c>
@@ -38735,7 +38782,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="340" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="12">
         <v>340</v>
       </c>
@@ -38818,7 +38865,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="341" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="12">
         <v>341</v>
       </c>
@@ -38901,7 +38948,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="342" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="12">
         <v>342</v>
       </c>
@@ -38984,7 +39031,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="343" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="12">
         <v>343</v>
       </c>
@@ -39067,7 +39114,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="344" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="12">
         <v>344</v>
       </c>
@@ -39150,7 +39197,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="345" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="12">
         <v>345</v>
       </c>
@@ -39233,7 +39280,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="346" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="12">
         <v>346</v>
       </c>
@@ -39316,7 +39363,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="347" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="12">
         <v>347</v>
       </c>
@@ -39399,7 +39446,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="348" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="12">
         <v>348</v>
       </c>
@@ -39482,7 +39529,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="349" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="12">
         <v>349</v>
       </c>
@@ -39565,7 +39612,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="350" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="12">
         <v>350</v>
       </c>
@@ -39648,7 +39695,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="351" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="12">
         <v>351</v>
       </c>
@@ -39731,7 +39778,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="352" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="12">
         <v>352</v>
       </c>
@@ -39814,7 +39861,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="353" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="12">
         <v>353</v>
       </c>
@@ -39897,7 +39944,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="354" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="12">
         <v>354</v>
       </c>
@@ -39980,7 +40027,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="355" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="12">
         <v>355</v>
       </c>
@@ -40063,7 +40110,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="356" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="12">
         <v>356</v>
       </c>
@@ -40146,7 +40193,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="357" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="12">
         <v>357</v>
       </c>
@@ -40229,7 +40276,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="358" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="12">
         <v>358</v>
       </c>
@@ -40312,7 +40359,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="359" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="12">
         <v>359</v>
       </c>
@@ -40395,7 +40442,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="360" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="12">
         <v>360</v>
       </c>
@@ -40478,7 +40525,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="361" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="12">
         <v>361</v>
       </c>
@@ -40561,7 +40608,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="362" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="12">
         <v>362</v>
       </c>
@@ -40644,7 +40691,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="363" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="12">
         <v>363</v>
       </c>
@@ -40727,7 +40774,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="364" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="12">
         <v>364</v>
       </c>
@@ -40810,7 +40857,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="365" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="12">
         <v>365</v>
       </c>
@@ -40893,7 +40940,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="366" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="12">
         <v>366</v>
       </c>
@@ -40976,7 +41023,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="367" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="12">
         <v>367</v>
       </c>
@@ -41059,7 +41106,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="368" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="12">
         <v>368</v>
       </c>
@@ -41142,7 +41189,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="369" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="12">
         <v>369</v>
       </c>
@@ -41225,7 +41272,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="370" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="12">
         <v>370</v>
       </c>
@@ -41308,7 +41355,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="371" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="12">
         <v>371</v>
       </c>
@@ -41391,7 +41438,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="372" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="12">
         <v>372</v>
       </c>
@@ -41474,7 +41521,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="373" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="12">
         <v>373</v>
       </c>
@@ -41557,7 +41604,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="374" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="12">
         <v>374</v>
       </c>
@@ -41640,7 +41687,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="375" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="12">
         <v>375</v>
       </c>
@@ -41723,7 +41770,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="376" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="12">
         <v>376</v>
       </c>
@@ -41806,7 +41853,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="377" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="12">
         <v>377</v>
       </c>
@@ -41889,7 +41936,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="378" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="12">
         <v>378</v>
       </c>
@@ -41972,7 +42019,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="379" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="12">
         <v>379</v>
       </c>
@@ -42055,7 +42102,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="380" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="12">
         <v>380</v>
       </c>
@@ -42138,7 +42185,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="381" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="12">
         <v>381</v>
       </c>
@@ -42221,7 +42268,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="382" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="12">
         <v>382</v>
       </c>
@@ -42304,7 +42351,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="383" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="12">
         <v>383</v>
       </c>
@@ -42387,7 +42434,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="384" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="12">
         <v>384</v>
       </c>
@@ -42470,7 +42517,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="385" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="12">
         <v>385</v>
       </c>
@@ -42553,7 +42600,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="386" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="12">
         <v>386</v>
       </c>
@@ -42636,7 +42683,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="387" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="12">
         <v>387</v>
       </c>
@@ -42719,7 +42766,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="388" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="12">
         <v>388</v>
       </c>
@@ -42802,7 +42849,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="389" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="12">
         <v>389</v>
       </c>
@@ -42885,7 +42932,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="390" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="12">
         <v>390</v>
       </c>
@@ -42968,7 +43015,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="391" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="12">
         <v>391</v>
       </c>
@@ -43051,7 +43098,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="392" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="12">
         <v>392</v>
       </c>
@@ -43134,7 +43181,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="393" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="12">
         <v>393</v>
       </c>
@@ -43217,7 +43264,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="394" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="12">
         <v>394</v>
       </c>
@@ -43300,7 +43347,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="395" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="12">
         <v>395</v>
       </c>
@@ -43383,7 +43430,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="396" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="12">
         <v>396</v>
       </c>
@@ -43466,7 +43513,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="397" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="12">
         <v>397</v>
       </c>
@@ -43549,7 +43596,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="398" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="12">
         <v>398</v>
       </c>
@@ -43632,7 +43679,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="399" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="12">
         <v>399</v>
       </c>
@@ -43715,7 +43762,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="400" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="12">
         <v>400</v>
       </c>
@@ -43798,7 +43845,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="401" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="12">
         <v>401</v>
       </c>
@@ -43881,7 +43928,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="402" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="12">
         <v>402</v>
       </c>
@@ -43964,7 +44011,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="403" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="12">
         <v>403</v>
       </c>
@@ -44047,7 +44094,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="404" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="12">
         <v>404</v>
       </c>
@@ -44130,7 +44177,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="405" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="12">
         <v>405</v>
       </c>
@@ -44213,7 +44260,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="406" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="12">
         <v>406</v>
       </c>
@@ -44296,7 +44343,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="407" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="12">
         <v>407</v>
       </c>
@@ -44379,7 +44426,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="408" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="12">
         <v>408</v>
       </c>
@@ -44462,7 +44509,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="409" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="12">
         <v>409</v>
       </c>
@@ -44545,7 +44592,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="410" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="12">
         <v>410</v>
       </c>
@@ -44628,7 +44675,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="411" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="12">
         <v>411</v>
       </c>
@@ -44711,7 +44758,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="412" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="12">
         <v>412</v>
       </c>
@@ -44794,7 +44841,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="413" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="12">
         <v>413</v>
       </c>
@@ -44877,7 +44924,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="414" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="12">
         <v>414</v>
       </c>
@@ -44960,7 +45007,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="415" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="12">
         <v>415</v>
       </c>
@@ -45043,7 +45090,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="416" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="12">
         <v>416</v>
       </c>
@@ -45126,7 +45173,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="417" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="12">
         <v>417</v>
       </c>
@@ -45209,7 +45256,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="418" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="12">
         <v>418</v>
       </c>
@@ -45292,7 +45339,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="419" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="12">
         <v>419</v>
       </c>
@@ -45375,7 +45422,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="420" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="12">
         <v>420</v>
       </c>
@@ -45458,7 +45505,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="421" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="12">
         <v>421</v>
       </c>
@@ -45541,7 +45588,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="422" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="12">
         <v>422</v>
       </c>
@@ -45624,7 +45671,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="423" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="12">
         <v>423</v>
       </c>
@@ -45707,7 +45754,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="424" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="12">
         <v>424</v>
       </c>
@@ -45790,7 +45837,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="425" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="12">
         <v>425</v>
       </c>
@@ -45873,7 +45920,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="426" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="12">
         <v>426</v>
       </c>
@@ -45956,7 +46003,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="427" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="12">
         <v>427</v>
       </c>
@@ -46039,7 +46086,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="428" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="12">
         <v>428</v>
       </c>
@@ -46122,7 +46169,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="429" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="12">
         <v>429</v>
       </c>
@@ -46205,7 +46252,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="430" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="12">
         <v>430</v>
       </c>
@@ -46288,7 +46335,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="431" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="12">
         <v>431</v>
       </c>
@@ -46371,7 +46418,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="432" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="12">
         <v>432</v>
       </c>
@@ -46454,7 +46501,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="433" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="12">
         <v>433</v>
       </c>
@@ -46537,7 +46584,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="434" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="12">
         <v>434</v>
       </c>
@@ -46620,7 +46667,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="435" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="12">
         <v>435</v>
       </c>
@@ -46703,7 +46750,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="436" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="12">
         <v>436</v>
       </c>
@@ -46786,7 +46833,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="437" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="12">
         <v>437</v>
       </c>
@@ -46869,7 +46916,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="438" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="12">
         <v>438</v>
       </c>
@@ -46952,7 +46999,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="439" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="12">
         <v>439</v>
       </c>
@@ -47035,7 +47082,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="440" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="12">
         <v>440</v>
       </c>
@@ -47118,7 +47165,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="441" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="12">
         <v>441</v>
       </c>
@@ -47201,7 +47248,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="442" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="12">
         <v>442</v>
       </c>
@@ -47284,7 +47331,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="443" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="12">
         <v>443</v>
       </c>
@@ -47367,7 +47414,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="444" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="12">
         <v>444</v>
       </c>
@@ -47450,7 +47497,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="445" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="12">
         <v>445</v>
       </c>
@@ -47533,7 +47580,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="446" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="12">
         <v>446</v>
       </c>
@@ -47616,7 +47663,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="447" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="12">
         <v>447</v>
       </c>
@@ -47699,7 +47746,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="448" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="12">
         <v>448</v>
       </c>
@@ -47782,7 +47829,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="449" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="12">
         <v>449</v>
       </c>
@@ -47865,7 +47912,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="450" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="12">
         <v>450</v>
       </c>
@@ -47948,7 +47995,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="451" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="12">
         <v>451</v>
       </c>
@@ -48031,7 +48078,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="452" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="12">
         <v>452</v>
       </c>
@@ -48114,7 +48161,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="453" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="12">
         <v>453</v>
       </c>
@@ -48197,7 +48244,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="454" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="12">
         <v>454</v>
       </c>
@@ -48280,7 +48327,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="455" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="12">
         <v>455</v>
       </c>
@@ -48363,7 +48410,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="456" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="12">
         <v>456</v>
       </c>
@@ -48446,7 +48493,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="457" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="12">
         <v>457</v>
       </c>
@@ -48529,7 +48576,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="458" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="12">
         <v>458</v>
       </c>
@@ -48612,7 +48659,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="459" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="12">
         <v>459</v>
       </c>
@@ -48695,7 +48742,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="460" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="12">
         <v>460</v>
       </c>
@@ -48778,7 +48825,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="461" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="12">
         <v>461</v>
       </c>
@@ -48861,7 +48908,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="462" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="12">
         <v>462</v>
       </c>
@@ -48944,7 +48991,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="463" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="12">
         <v>463</v>
       </c>
@@ -49027,7 +49074,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="464" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="12">
         <v>464</v>
       </c>
@@ -49110,7 +49157,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="465" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="12">
         <v>465</v>
       </c>
@@ -49193,7 +49240,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="466" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="12">
         <v>466</v>
       </c>
@@ -49276,7 +49323,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="467" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="12">
         <v>467</v>
       </c>
@@ -49359,7 +49406,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="468" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="12">
         <v>468</v>
       </c>
@@ -49442,7 +49489,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="469" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="12">
         <v>469</v>
       </c>
@@ -49525,7 +49572,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="470" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="12">
         <v>470</v>
       </c>
@@ -49608,7 +49655,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="471" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="12">
         <v>471</v>
       </c>
@@ -49691,7 +49738,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="472" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="12">
         <v>472</v>
       </c>
@@ -49774,7 +49821,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="473" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="12">
         <v>473</v>
       </c>
@@ -49857,7 +49904,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="474" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="12">
         <v>474</v>
       </c>
@@ -49940,7 +49987,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="475" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="12">
         <v>475</v>
       </c>
@@ -50023,7 +50070,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="476" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="12">
         <v>476</v>
       </c>
@@ -50106,7 +50153,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="477" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="12">
         <v>477</v>
       </c>
@@ -50189,7 +50236,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="478" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="12">
         <v>478</v>
       </c>
@@ -50272,7 +50319,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="479" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="12">
         <v>479</v>
       </c>
@@ -50355,7 +50402,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="480" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="12">
         <v>480</v>
       </c>
@@ -50438,7 +50485,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="481" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="12">
         <v>481</v>
       </c>
@@ -50521,7 +50568,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="482" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="12">
         <v>482</v>
       </c>
@@ -50604,7 +50651,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="483" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="12">
         <v>483</v>
       </c>
@@ -50687,7 +50734,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="484" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="12">
         <v>484</v>
       </c>
@@ -50770,7 +50817,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="485" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="12">
         <v>485</v>
       </c>
@@ -50853,7 +50900,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="486" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="12">
         <v>486</v>
       </c>
@@ -50936,7 +50983,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="487" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="12">
         <v>487</v>
       </c>
@@ -51019,7 +51066,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="488" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="12">
         <v>488</v>
       </c>
@@ -51102,7 +51149,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="489" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="12">
         <v>489</v>
       </c>
@@ -51185,7 +51232,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="490" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="12">
         <v>490</v>
       </c>
@@ -51268,7 +51315,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="491" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="12">
         <v>491</v>
       </c>
@@ -51351,7 +51398,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="492" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="12">
         <v>492</v>
       </c>
@@ -51434,7 +51481,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="493" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="12">
         <v>493</v>
       </c>
@@ -51517,7 +51564,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="494" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="12">
         <v>494</v>
       </c>
@@ -51600,7 +51647,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="495" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="12">
         <v>495</v>
       </c>
@@ -51683,7 +51730,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="496" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="12">
         <v>496</v>
       </c>
@@ -51766,7 +51813,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="497" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="12">
         <v>497</v>
       </c>
@@ -51849,7 +51896,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="498" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="12">
         <v>498</v>
       </c>
@@ -51932,7 +51979,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="499" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="12">
         <v>499</v>
       </c>
@@ -52015,7 +52062,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="500" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="12">
         <v>500</v>
       </c>
@@ -52098,7 +52145,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="501" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="12">
         <v>501</v>
       </c>
@@ -52181,7 +52228,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="502" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="12">
         <v>502</v>
       </c>
@@ -52264,7 +52311,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="503" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="12">
         <v>503</v>
       </c>
@@ -52347,7 +52394,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="504" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="12">
         <v>504</v>
       </c>
@@ -52430,7 +52477,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="505" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="12">
         <v>505</v>
       </c>
@@ -52513,7 +52560,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="506" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="12">
         <v>506</v>
       </c>
@@ -52596,7 +52643,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="507" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="12">
         <v>507</v>
       </c>
@@ -52679,7 +52726,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="508" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="12">
         <v>508</v>
       </c>
@@ -52762,7 +52809,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="509" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="12">
         <v>509</v>
       </c>
@@ -52845,7 +52892,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="510" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="12">
         <v>510</v>
       </c>
@@ -52928,7 +52975,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="511" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="12">
         <v>511</v>
       </c>
@@ -53011,7 +53058,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="512" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="12">
         <v>512</v>
       </c>
@@ -53094,7 +53141,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="513" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="12">
         <v>513</v>
       </c>
@@ -53177,7 +53224,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="514" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="12">
         <v>514</v>
       </c>
@@ -53260,7 +53307,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="515" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="12">
         <v>515</v>
       </c>
@@ -53343,7 +53390,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="516" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="12">
         <v>516</v>
       </c>
@@ -53426,7 +53473,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="517" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="12">
         <v>517</v>
       </c>
@@ -53509,7 +53556,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="518" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="12">
         <v>518</v>
       </c>
@@ -53592,7 +53639,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="519" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="12">
         <v>519</v>
       </c>
@@ -53675,7 +53722,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="520" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="12">
         <v>520</v>
       </c>
@@ -53758,7 +53805,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="521" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="12">
         <v>521</v>
       </c>
@@ -53841,7 +53888,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="522" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="12">
         <v>522</v>
       </c>
@@ -53924,7 +53971,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="523" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="12">
         <v>523</v>
       </c>
@@ -54007,7 +54054,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="524" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="12">
         <v>524</v>
       </c>
@@ -54090,7 +54137,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="525" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="12">
         <v>525</v>
       </c>
@@ -54173,7 +54220,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="526" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="12">
         <v>526</v>
       </c>
@@ -54256,7 +54303,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="527" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="12">
         <v>527</v>
       </c>
@@ -54339,7 +54386,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="528" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="12">
         <v>528</v>
       </c>
@@ -54422,7 +54469,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="529" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="12">
         <v>529</v>
       </c>
@@ -54505,7 +54552,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="530" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="12">
         <v>530</v>
       </c>
@@ -54588,7 +54635,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="531" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="12">
         <v>531</v>
       </c>
@@ -54671,7 +54718,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="532" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="12">
         <v>532</v>
       </c>
@@ -54754,7 +54801,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="533" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="12">
         <v>533</v>
       </c>
@@ -54837,7 +54884,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="534" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="12">
         <v>534</v>
       </c>
@@ -54920,7 +54967,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="535" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="12">
         <v>535</v>
       </c>
@@ -55003,7 +55050,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="536" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="12">
         <v>536</v>
       </c>
@@ -55086,7 +55133,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="537" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="12">
         <v>537</v>
       </c>
@@ -55169,7 +55216,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="538" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="12">
         <v>538</v>
       </c>
@@ -55252,7 +55299,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="539" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="12">
         <v>539</v>
       </c>
@@ -55335,7 +55382,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="540" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="12">
         <v>540</v>
       </c>
@@ -55418,7 +55465,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="541" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="12">
         <v>541</v>
       </c>
@@ -55501,7 +55548,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="542" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="12">
         <v>542</v>
       </c>
@@ -55584,7 +55631,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="543" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="12">
         <v>543</v>
       </c>
@@ -55667,7 +55714,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="544" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="12">
         <v>544</v>
       </c>
@@ -55750,7 +55797,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="545" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="12">
         <v>545</v>
       </c>
@@ -55833,7 +55880,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="546" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="12">
         <v>546</v>
       </c>
@@ -55916,7 +55963,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="547" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="12">
         <v>547</v>
       </c>
@@ -55999,7 +56046,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="548" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="12">
         <v>548</v>
       </c>
@@ -56082,7 +56129,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="549" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="12">
         <v>549</v>
       </c>
@@ -56165,7 +56212,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="550" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="12">
         <v>550</v>
       </c>
@@ -56248,7 +56295,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="551" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="12">
         <v>551</v>
       </c>
@@ -56331,7 +56378,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="552" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="12">
         <v>552</v>
       </c>
@@ -56414,7 +56461,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="553" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="12">
         <v>553</v>
       </c>
@@ -56497,7 +56544,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="554" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="12">
         <v>554</v>
       </c>
@@ -56580,7 +56627,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="555" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="12">
         <v>555</v>
       </c>
@@ -56663,7 +56710,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="556" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="12">
         <v>556</v>
       </c>
@@ -56746,7 +56793,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="557" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="12">
         <v>557</v>
       </c>
@@ -56829,7 +56876,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="558" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="12">
         <v>558</v>
       </c>
@@ -56912,7 +56959,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="559" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="12">
         <v>559</v>
       </c>
@@ -56995,7 +57042,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="560" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="12">
         <v>560</v>
       </c>
@@ -57078,7 +57125,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="561" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="12">
         <v>561</v>
       </c>
@@ -57161,7 +57208,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="562" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="12">
         <v>562</v>
       </c>
@@ -57244,7 +57291,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="563" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="12">
         <v>563</v>
       </c>
@@ -57327,7 +57374,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="564" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="12">
         <v>564</v>
       </c>
@@ -57410,7 +57457,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="565" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="12">
         <v>565</v>
       </c>
@@ -57493,7 +57540,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="566" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="12">
         <v>566</v>
       </c>
@@ -57576,7 +57623,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="567" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="12">
         <v>567</v>
       </c>
@@ -57659,7 +57706,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="568" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="12">
         <v>568</v>
       </c>
@@ -57742,7 +57789,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="569" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="12">
         <v>569</v>
       </c>
@@ -57825,7 +57872,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="570" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="12">
         <v>570</v>
       </c>
@@ -57908,7 +57955,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="571" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="12">
         <v>571</v>
       </c>
@@ -57991,7 +58038,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="572" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="12">
         <v>572</v>
       </c>
@@ -58074,7 +58121,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="573" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="12">
         <v>573</v>
       </c>
@@ -58157,7 +58204,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="574" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="12">
         <v>574</v>
       </c>
@@ -58240,7 +58287,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="575" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="12">
         <v>575</v>
       </c>
@@ -58323,7 +58370,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="576" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="12">
         <v>576</v>
       </c>
@@ -58406,7 +58453,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="577" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="12">
         <v>577</v>
       </c>
@@ -58489,7 +58536,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="578" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="12">
         <v>578</v>
       </c>
@@ -58572,7 +58619,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="579" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="12">
         <v>579</v>
       </c>
@@ -58655,7 +58702,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="580" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="12">
         <v>580</v>
       </c>
@@ -58738,7 +58785,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="581" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="12">
         <v>581</v>
       </c>
@@ -58821,7 +58868,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="582" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="12">
         <v>582</v>
       </c>
@@ -58904,7 +58951,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="583" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="12">
         <v>583</v>
       </c>
@@ -58987,7 +59034,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="584" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="12">
         <v>584</v>
       </c>
@@ -59070,7 +59117,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="585" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="12">
         <v>585</v>
       </c>
@@ -59153,7 +59200,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="586" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="12">
         <v>586</v>
       </c>
@@ -59236,7 +59283,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="587" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="12">
         <v>587</v>
       </c>
@@ -59319,7 +59366,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="588" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="12">
         <v>588</v>
       </c>
@@ -59402,7 +59449,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="589" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="12">
         <v>589</v>
       </c>
@@ -59485,7 +59532,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="590" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="12">
         <v>590</v>
       </c>
@@ -59568,7 +59615,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="591" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="12">
         <v>591</v>
       </c>
@@ -59651,7 +59698,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="592" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="12">
         <v>592</v>
       </c>
@@ -59734,7 +59781,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="593" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="12">
         <v>593</v>
       </c>
@@ -59817,7 +59864,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="594" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="12">
         <v>594</v>
       </c>
@@ -59900,7 +59947,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="595" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="12">
         <v>595</v>
       </c>
@@ -59983,7 +60030,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="596" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="12">
         <v>596</v>
       </c>
@@ -60066,7 +60113,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="597" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="12">
         <v>597</v>
       </c>
@@ -60149,7 +60196,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="598" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="12">
         <v>598</v>
       </c>
@@ -60232,7 +60279,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="599" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="12">
         <v>599</v>
       </c>
@@ -60315,7 +60362,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="600" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="12">
         <v>600</v>
       </c>
@@ -60398,7 +60445,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="601" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="12">
         <v>601</v>
       </c>
@@ -60481,7 +60528,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="602" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="12">
         <v>602</v>
       </c>
@@ -60564,7 +60611,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="603" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="12">
         <v>603</v>
       </c>
@@ -60647,7 +60694,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="604" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="12">
         <v>604</v>
       </c>
@@ -60730,7 +60777,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="605" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="12">
         <v>605</v>
       </c>
@@ -60813,7 +60860,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="606" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="12">
         <v>606</v>
       </c>
@@ -60896,7 +60943,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="607" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="12">
         <v>607</v>
       </c>
@@ -60979,7 +61026,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="608" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="12">
         <v>608</v>
       </c>
@@ -61062,7 +61109,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="609" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="12">
         <v>609</v>
       </c>
@@ -61145,7 +61192,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="610" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="12">
         <v>610</v>
       </c>
@@ -61228,7 +61275,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="611" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="12">
         <v>611</v>
       </c>
@@ -61311,7 +61358,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="612" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="12">
         <v>612</v>
       </c>
@@ -61394,7 +61441,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="613" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="12">
         <v>613</v>
       </c>
@@ -61477,7 +61524,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="614" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="12">
         <v>614</v>
       </c>
@@ -61560,7 +61607,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="615" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="12">
         <v>615</v>
       </c>
@@ -61643,7 +61690,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="616" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="12">
         <v>616</v>
       </c>
@@ -61726,7 +61773,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="617" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="12">
         <v>617</v>
       </c>
@@ -61809,7 +61856,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="618" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="12">
         <v>618</v>
       </c>
@@ -61892,7 +61939,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="619" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="12">
         <v>619</v>
       </c>
@@ -61975,7 +62022,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="620" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="12">
         <v>620</v>
       </c>
@@ -62058,7 +62105,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="621" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="12">
         <v>621</v>
       </c>
@@ -62141,7 +62188,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="622" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="12">
         <v>622</v>
       </c>
@@ -62224,7 +62271,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="623" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="12">
         <v>623</v>
       </c>
@@ -62307,7 +62354,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="624" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="12">
         <v>624</v>
       </c>
@@ -62390,7 +62437,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="625" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="12">
         <v>625</v>
       </c>
@@ -62473,7 +62520,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="626" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="12">
         <v>626</v>
       </c>
@@ -62556,7 +62603,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="627" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="12">
         <v>627</v>
       </c>
@@ -62639,7 +62686,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="628" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="12">
         <v>628</v>
       </c>
@@ -62722,7 +62769,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="629" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="12">
         <v>629</v>
       </c>
@@ -62805,7 +62852,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="630" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="12">
         <v>630</v>
       </c>
@@ -62888,7 +62935,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="631" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="12">
         <v>631</v>
       </c>
@@ -62971,7 +63018,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="632" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="12">
         <v>632</v>
       </c>
@@ -63054,7 +63101,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="633" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="12">
         <v>633</v>
       </c>
@@ -63137,7 +63184,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="634" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="12">
         <v>634</v>
       </c>
@@ -63220,7 +63267,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="635" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="12">
         <v>635</v>
       </c>
@@ -63303,7 +63350,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="636" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="12">
         <v>636</v>
       </c>
@@ -63386,7 +63433,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="637" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="12">
         <v>637</v>
       </c>
@@ -63469,7 +63516,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="638" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="12">
         <v>638</v>
       </c>
@@ -63552,7 +63599,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="639" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="12">
         <v>639</v>
       </c>
@@ -63635,7 +63682,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="640" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="12">
         <v>640</v>
       </c>
@@ -63718,7 +63765,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="641" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="12">
         <v>641</v>
       </c>
@@ -63801,7 +63848,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="642" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="12">
         <v>642</v>
       </c>
@@ -63884,7 +63931,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="643" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="12">
         <v>643</v>
       </c>
@@ -63967,7 +64014,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="644" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="12">
         <v>644</v>
       </c>
@@ -64050,7 +64097,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="645" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="12">
         <v>645</v>
       </c>
@@ -64133,7 +64180,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="646" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="12">
         <v>646</v>
       </c>
@@ -64216,7 +64263,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="647" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="12">
         <v>647</v>
       </c>
@@ -64299,7 +64346,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="648" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="12">
         <v>648</v>
       </c>
@@ -64382,7 +64429,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="649" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="12">
         <v>649</v>
       </c>
@@ -64465,7 +64512,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="650" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="12">
         <v>650</v>
       </c>
@@ -64548,7 +64595,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="651" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="12">
         <v>651</v>
       </c>
@@ -64631,7 +64678,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="652" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="12">
         <v>652</v>
       </c>
@@ -64714,7 +64761,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="653" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="12">
         <v>653</v>
       </c>
@@ -64797,7 +64844,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="654" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="12">
         <v>654</v>
       </c>
@@ -64880,7 +64927,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="655" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="12">
         <v>655</v>
       </c>
@@ -64963,7 +65010,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="656" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="12">
         <v>656</v>
       </c>
@@ -65046,7 +65093,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="657" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="12">
         <v>657</v>
       </c>
@@ -65129,7 +65176,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="658" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="12">
         <v>658</v>
       </c>
@@ -65212,7 +65259,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="659" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="12">
         <v>659</v>
       </c>
@@ -65295,7 +65342,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="660" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="12">
         <v>660</v>
       </c>
@@ -65378,7 +65425,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="661" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="12">
         <v>661</v>
       </c>
@@ -65461,7 +65508,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="662" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="12">
         <v>662</v>
       </c>
@@ -65544,7 +65591,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="663" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="12">
         <v>663</v>
       </c>
@@ -65627,7 +65674,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="664" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="12">
         <v>664</v>
       </c>
@@ -65710,7 +65757,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="665" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="12">
         <v>665</v>
       </c>
@@ -65793,7 +65840,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="666" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="12">
         <v>666</v>
       </c>
@@ -65876,7 +65923,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="667" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="12">
         <v>667</v>
       </c>
@@ -65959,7 +66006,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="668" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="12">
         <v>668</v>
       </c>
@@ -66042,7 +66089,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="669" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="12">
         <v>669</v>
       </c>
@@ -66125,7 +66172,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="670" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="12">
         <v>670</v>
       </c>
@@ -66208,7 +66255,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="671" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="12">
         <v>671</v>
       </c>
@@ -66291,7 +66338,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="672" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="12">
         <v>672</v>
       </c>
@@ -66374,7 +66421,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="673" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="12">
         <v>673</v>
       </c>
@@ -66457,7 +66504,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="674" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="12">
         <v>674</v>
       </c>
@@ -66540,7 +66587,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="675" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="12">
         <v>675</v>
       </c>
@@ -66623,7 +66670,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="676" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="12">
         <v>676</v>
       </c>
@@ -66706,7 +66753,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="677" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="12">
         <v>677</v>
       </c>
@@ -66789,7 +66836,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="678" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="12">
         <v>678</v>
       </c>
@@ -66872,7 +66919,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="679" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="12">
         <v>679</v>
       </c>
@@ -66955,7 +67002,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="680" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="12">
         <v>680</v>
       </c>
@@ -67038,7 +67085,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="681" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="12">
         <v>681</v>
       </c>
@@ -67121,7 +67168,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="682" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="12">
         <v>682</v>
       </c>
@@ -67204,7 +67251,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="683" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="12">
         <v>683</v>
       </c>
@@ -67287,7 +67334,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="684" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="12">
         <v>684</v>
       </c>
@@ -67370,7 +67417,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="685" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="12">
         <v>685</v>
       </c>
@@ -67453,7 +67500,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="686" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="12">
         <v>686</v>
       </c>
@@ -67536,7 +67583,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="687" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="12">
         <v>687</v>
       </c>
@@ -67619,7 +67666,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="688" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="12">
         <v>688</v>
       </c>
@@ -67702,7 +67749,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="689" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="12">
         <v>689</v>
       </c>
@@ -67785,7 +67832,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="690" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="12">
         <v>690</v>
       </c>
@@ -67868,7 +67915,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="691" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="12">
         <v>691</v>
       </c>
@@ -67951,7 +67998,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="692" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="12">
         <v>692</v>
       </c>
@@ -68034,7 +68081,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="693" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="12">
         <v>693</v>
       </c>
@@ -68117,7 +68164,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="694" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="12">
         <v>694</v>
       </c>
@@ -68200,7 +68247,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="695" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="12">
         <v>695</v>
       </c>
@@ -68283,7 +68330,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="696" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="12">
         <v>696</v>
       </c>
@@ -68366,7 +68413,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="697" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="12">
         <v>697</v>
       </c>
@@ -68449,7 +68496,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="698" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="12">
         <v>698</v>
       </c>
@@ -68532,7 +68579,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="699" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="12">
         <v>699</v>
       </c>
@@ -68615,7 +68662,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="700" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="12">
         <v>700</v>
       </c>
@@ -68698,7 +68745,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="701" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="12">
         <v>701</v>
       </c>
@@ -68781,7 +68828,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="702" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="12">
         <v>702</v>
       </c>
@@ -68864,7 +68911,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="703" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="12">
         <v>703</v>
       </c>
@@ -68947,7 +68994,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="704" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="12">
         <v>704</v>
       </c>
@@ -69030,7 +69077,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="705" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="12">
         <v>705</v>
       </c>
@@ -69113,7 +69160,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="706" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="12">
         <v>706</v>
       </c>
@@ -69196,7 +69243,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="707" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="12">
         <v>707</v>
       </c>
@@ -69279,7 +69326,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="708" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="12">
         <v>708</v>
       </c>
@@ -69362,7 +69409,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="709" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="12">
         <v>709</v>
       </c>
@@ -69445,7 +69492,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="710" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="12">
         <v>710</v>
       </c>
@@ -69528,7 +69575,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="711" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="12">
         <v>711</v>
       </c>
@@ -69611,7 +69658,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="712" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="12">
         <v>712</v>
       </c>
@@ -69694,7 +69741,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="713" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="12">
         <v>713</v>
       </c>
@@ -69777,7 +69824,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="714" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="12">
         <v>714</v>
       </c>
@@ -69860,7 +69907,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="715" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="12">
         <v>715</v>
       </c>
@@ -69943,7 +69990,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="716" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="12">
         <v>716</v>
       </c>
@@ -70026,7 +70073,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="717" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="12">
         <v>717</v>
       </c>
@@ -70109,7 +70156,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="718" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="12">
         <v>718</v>
       </c>
@@ -70192,7 +70239,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="719" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="12">
         <v>719</v>
       </c>
@@ -70275,7 +70322,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="720" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="12">
         <v>720</v>
       </c>
@@ -70358,7 +70405,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="721" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="12">
         <v>721</v>
       </c>
@@ -70441,7 +70488,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="722" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="12">
         <v>722</v>
       </c>
@@ -70524,7 +70571,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="723" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="12">
         <v>723</v>
       </c>
@@ -70607,7 +70654,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="724" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="12">
         <v>724</v>
       </c>
@@ -70690,7 +70737,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="725" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="12">
         <v>725</v>
       </c>
@@ -70773,7 +70820,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="726" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="12">
         <v>726</v>
       </c>
@@ -70856,7 +70903,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="727" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="12">
         <v>727</v>
       </c>
@@ -70939,7 +70986,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="728" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="12">
         <v>728</v>
       </c>
@@ -71022,7 +71069,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="729" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="12">
         <v>729</v>
       </c>
@@ -71105,7 +71152,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="730" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="12">
         <v>730</v>
       </c>
@@ -71188,7 +71235,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="731" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="12">
         <v>731</v>
       </c>
@@ -71271,7 +71318,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="732" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="12">
         <v>732</v>
       </c>
@@ -71360,65 +71407,65 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:I2 N2:Q2 AB2:XFD2 P2:AA732 D3:E3 D4:D732">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 F1">
-    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="6" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_5I.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_5I.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8820305D-A4F1-4440-9F36-799A2D0EE256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E222F72-9BF5-4F30-B59C-BEFF293FF385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19847" uniqueCount="1799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19919" uniqueCount="1801">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -5488,6 +5488,12 @@
   </si>
   <si>
     <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
   </si>
 </sst>
 </file>
@@ -6097,39 +6103,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8576210E-162F-453B-B886-CD2163C7562E}"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <b val="0"/>
@@ -6262,6 +6236,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -6272,13 +6254,10 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6627,14 +6606,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFEA285-1F1C-49D4-8690-0B8CB6A5C474}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
@@ -6645,7 +6624,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>19</v>
       </c>
@@ -6656,7 +6635,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
@@ -6667,7 +6646,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -6678,7 +6657,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
@@ -6690,7 +6669,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
@@ -6702,7 +6681,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
@@ -6713,7 +6692,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
@@ -6724,7 +6703,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
@@ -6735,7 +6714,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
@@ -6746,7 +6725,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>24</v>
       </c>
@@ -6757,7 +6736,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
@@ -6768,7 +6747,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -6779,7 +6758,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
@@ -6790,7 +6769,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
@@ -6801,7 +6780,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
@@ -6812,7 +6791,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>12</v>
       </c>
@@ -6823,19 +6802,19 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="4">
         <f ca="1">NOW()</f>
-        <v>46249.319243749997</v>
+        <v>46253.5880412037</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>1540</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>1548</v>
       </c>
@@ -6846,7 +6825,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>1544</v>
       </c>
@@ -6858,7 +6837,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>1549</v>
       </c>
@@ -6870,7 +6849,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>18</v>
       </c>
@@ -6881,7 +6860,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>30</v>
       </c>
@@ -6892,7 +6871,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
@@ -6903,7 +6882,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
@@ -6914,7 +6893,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="45" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="45" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>1537</v>
       </c>
@@ -6925,7 +6904,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>1757</v>
       </c>
@@ -6936,7 +6915,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>1759</v>
       </c>
@@ -6947,7 +6926,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>1761</v>
       </c>
@@ -6958,7 +6937,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
         <v>1763</v>
       </c>
@@ -6969,7 +6948,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
         <v>1765</v>
       </c>
@@ -6980,7 +6959,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
         <v>1767</v>
       </c>
@@ -6991,7 +6970,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
         <v>1769</v>
       </c>
@@ -7002,7 +6981,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
         <v>1771</v>
       </c>
@@ -7013,7 +6992,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
         <v>1773</v>
       </c>
@@ -7024,7 +7003,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
         <v>1775</v>
       </c>
@@ -7035,7 +7014,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="72" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
         <v>1777</v>
       </c>
@@ -7046,7 +7025,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>1779</v>
       </c>
@@ -7057,7 +7036,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="76" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="76" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7" t="s">
         <v>1781</v>
       </c>
@@ -7083,35 +7062,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A90C8D-F4F0-474F-8F2D-D62CBC6EB14C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA36"/>
-  <sheetFormatPr defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC36"/>
+  <sheetFormatPr defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.796875" style="65" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.796875" style="32" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="32" customWidth="1"/>
-    <col min="4" max="4" width="8.69921875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="12.296875" style="32" customWidth="1"/>
-    <col min="6" max="6" width="15.69921875" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.69921875" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="32" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.6640625" style="32" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.796875" customWidth="1"/>
-    <col min="15" max="15" width="15.296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="75.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.19921875" customWidth="1"/>
-    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="9.19921875" customWidth="1"/>
-    <col min="21" max="21" width="10" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="30.69921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="35.796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11" customWidth="1"/>
-    <col min="27" max="27" width="64.796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="75.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="61.33203125" customWidth="1"/>
+    <col min="18" max="18" width="54.1640625" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7" customWidth="1"/>
+    <col min="21" max="21" width="9.1640625" customWidth="1"/>
+    <col min="22" max="22" width="10" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="25.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="25.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>1482</v>
       </c>
@@ -7163,38 +7144,44 @@
       <c r="Q1" s="23" t="s">
         <v>1502</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="41" t="s">
+        <v>1535</v>
+      </c>
+      <c r="S1" s="24" t="s">
         <v>1526</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="T1" s="23" t="s">
         <v>1484</v>
       </c>
-      <c r="T1" s="23" t="s">
+      <c r="U1" s="23" t="s">
         <v>1503</v>
       </c>
-      <c r="U1" s="23" t="s">
+      <c r="V1" s="23" t="s">
         <v>1486</v>
       </c>
-      <c r="V1" s="23" t="s">
+      <c r="W1" s="23" t="s">
         <v>1485</v>
       </c>
-      <c r="W1" s="66" t="s">
+      <c r="X1" s="66" t="s">
         <v>1504</v>
       </c>
-      <c r="X1" s="39" t="s">
+      <c r="Y1" s="39" t="s">
         <v>1533</v>
       </c>
-      <c r="Y1" s="23" t="s">
+      <c r="Z1" s="39" t="s">
+        <v>1799</v>
+      </c>
+      <c r="AA1" s="23" t="s">
         <v>1534</v>
       </c>
-      <c r="Z1" s="23" t="s">
+      <c r="AB1" s="23" t="s">
+        <v>1800</v>
+      </c>
+      <c r="AC1" s="23" t="s">
         <v>1505</v>
       </c>
-      <c r="AA1" s="41" t="s">
-        <v>1535</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -7250,42 +7237,48 @@
       <c r="Q2" s="58" t="s">
         <v>1719</v>
       </c>
-      <c r="R2" s="42" t="s">
+      <c r="R2" s="59" t="s">
+        <v>1720</v>
+      </c>
+      <c r="S2" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="40" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="T2" s="40" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T2" s="40" t="str">
+      <c r="U2" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U2" s="58" t="str">
+      <c r="V2" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V2" s="42" t="s">
+      <c r="W2" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W2" s="68" t="str">
-        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+      <c r="X2" s="68" t="str">
+        <f t="shared" ref="X2:X14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
-      <c r="X2" s="42" t="s">
+      <c r="Y2" s="42" t="s">
         <v>1794</v>
       </c>
-      <c r="Y2" s="42" t="s">
+      <c r="Z2" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA2" s="42" t="s">
         <v>1795</v>
       </c>
-      <c r="Z2" s="42" t="s">
+      <c r="AB2" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC2" s="42" t="s">
         <v>1552</v>
       </c>
-      <c r="AA2" s="59" t="s">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -7341,42 +7334,48 @@
       <c r="Q3" s="58" t="s">
         <v>1722</v>
       </c>
-      <c r="R3" s="42" t="s">
+      <c r="R3" s="59" t="s">
+        <v>1723</v>
+      </c>
+      <c r="S3" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="40" t="str">
+      <c r="T3" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T3" s="40" t="str">
+      <c r="U3" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U3" s="58" t="str">
+      <c r="V3" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V3" s="42" t="s">
+      <c r="W3" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W3" s="68" t="str">
+      <c r="X3" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-3</v>
       </c>
-      <c r="X3" s="42" t="s">
+      <c r="Y3" s="42" t="s">
         <v>1796</v>
       </c>
-      <c r="Y3" s="42" t="s">
+      <c r="Z3" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA3" s="42" t="s">
         <v>1797</v>
       </c>
-      <c r="Z3" s="42" t="s">
+      <c r="AB3" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC3" s="42" t="s">
         <v>1553</v>
       </c>
-      <c r="AA3" s="59" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -7432,42 +7431,48 @@
       <c r="Q4" s="58" t="s">
         <v>1725</v>
       </c>
-      <c r="R4" s="42" t="s">
+      <c r="R4" s="59" t="s">
+        <v>1726</v>
+      </c>
+      <c r="S4" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S4" s="40" t="str">
+      <c r="T4" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T4" s="40" t="str">
+      <c r="U4" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U4" s="58" t="str">
+      <c r="V4" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V4" s="42" t="s">
+      <c r="W4" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W4" s="68" t="str">
+      <c r="X4" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="X4" s="42" t="s">
+      <c r="Y4" s="42" t="s">
         <v>1787</v>
       </c>
-      <c r="Y4" s="42" t="s">
+      <c r="Z4" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA4" s="42" t="s">
         <v>1788</v>
       </c>
-      <c r="Z4" s="42" t="s">
+      <c r="AB4" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC4" s="42" t="s">
         <v>1554</v>
       </c>
-      <c r="AA4" s="59" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -7523,42 +7528,48 @@
       <c r="Q5" s="58" t="s">
         <v>1728</v>
       </c>
-      <c r="R5" s="42" t="s">
+      <c r="R5" s="59" t="s">
+        <v>1729</v>
+      </c>
+      <c r="S5" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="40" t="str">
+      <c r="T5" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T5" s="40" t="str">
+      <c r="U5" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U5" s="58" t="str">
+      <c r="V5" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V5" s="42" t="s">
+      <c r="W5" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W5" s="68" t="str">
+      <c r="X5" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-5</v>
       </c>
-      <c r="X5" s="42" t="s">
+      <c r="Y5" s="42" t="s">
         <v>1789</v>
       </c>
-      <c r="Y5" s="42" t="s">
+      <c r="Z5" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA5" s="42" t="s">
         <v>1790</v>
       </c>
-      <c r="Z5" s="42" t="s">
+      <c r="AB5" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC5" s="42" t="s">
         <v>1555</v>
       </c>
-      <c r="AA5" s="59" t="s">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -7614,42 +7625,48 @@
       <c r="Q6" s="58" t="s">
         <v>1731</v>
       </c>
-      <c r="R6" s="42" t="s">
+      <c r="R6" s="59" t="s">
+        <v>1732</v>
+      </c>
+      <c r="S6" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S6" s="40" t="str">
+      <c r="T6" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T6" s="40" t="str">
+      <c r="U6" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U6" s="58" t="str">
+      <c r="V6" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V6" s="42" t="s">
+      <c r="W6" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W6" s="68" t="str">
+      <c r="X6" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="X6" s="42" t="s">
+      <c r="Y6" s="42" t="s">
         <v>1787</v>
       </c>
-      <c r="Y6" s="42" t="s">
+      <c r="Z6" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA6" s="42" t="s">
         <v>1788</v>
       </c>
-      <c r="Z6" s="42" t="s">
+      <c r="AB6" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC6" s="42" t="s">
         <v>1556</v>
       </c>
-      <c r="AA6" s="59" t="s">
-        <v>1732</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -7705,42 +7722,48 @@
       <c r="Q7" s="58" t="s">
         <v>1734</v>
       </c>
-      <c r="R7" s="42" t="s">
+      <c r="R7" s="59" t="s">
+        <v>1735</v>
+      </c>
+      <c r="S7" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S7" s="40" t="str">
+      <c r="T7" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T7" s="40" t="str">
+      <c r="U7" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U7" s="58" t="str">
+      <c r="V7" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V7" s="42" t="s">
+      <c r="W7" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W7" s="68" t="str">
+      <c r="X7" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="X7" s="42" t="s">
-        <v>1787</v>
-      </c>
       <c r="Y7" s="42" t="s">
         <v>1787</v>
       </c>
       <c r="Z7" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA7" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AB7" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC7" s="42" t="s">
         <v>1557</v>
       </c>
-      <c r="AA7" s="59" t="s">
-        <v>1735</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -7796,42 +7819,48 @@
       <c r="Q8" s="58" t="s">
         <v>1737</v>
       </c>
-      <c r="R8" s="42" t="s">
+      <c r="R8" s="59" t="s">
+        <v>1738</v>
+      </c>
+      <c r="S8" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="40" t="str">
+      <c r="T8" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T8" s="40" t="str">
+      <c r="U8" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U8" s="58" t="str">
+      <c r="V8" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V8" s="42" t="s">
+      <c r="W8" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W8" s="68" t="str">
+      <c r="X8" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="X8" s="42" t="s">
-        <v>1787</v>
-      </c>
       <c r="Y8" s="42" t="s">
         <v>1787</v>
       </c>
       <c r="Z8" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA8" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AB8" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC8" s="42" t="s">
         <v>1558</v>
       </c>
-      <c r="AA8" s="59" t="s">
-        <v>1738</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -7887,42 +7916,48 @@
       <c r="Q9" s="58" t="s">
         <v>1740</v>
       </c>
-      <c r="R9" s="42" t="s">
+      <c r="R9" s="59" t="s">
+        <v>1741</v>
+      </c>
+      <c r="S9" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S9" s="40" t="str">
+      <c r="T9" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T9" s="40" t="str">
+      <c r="U9" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U9" s="58" t="str">
+      <c r="V9" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V9" s="42" t="s">
+      <c r="W9" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W9" s="68" t="str">
+      <c r="X9" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="X9" s="42" t="s">
-        <v>1787</v>
-      </c>
       <c r="Y9" s="42" t="s">
         <v>1787</v>
       </c>
       <c r="Z9" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA9" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AB9" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC9" s="42" t="s">
         <v>1559</v>
       </c>
-      <c r="AA9" s="59" t="s">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -7978,42 +8013,48 @@
       <c r="Q10" s="58" t="s">
         <v>1743</v>
       </c>
-      <c r="R10" s="42" t="s">
+      <c r="R10" s="59" t="s">
+        <v>1744</v>
+      </c>
+      <c r="S10" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S10" s="40" t="str">
+      <c r="T10" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T10" s="40" t="str">
+      <c r="U10" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U10" s="58" t="str">
+      <c r="V10" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V10" s="42" t="s">
+      <c r="W10" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W10" s="68" t="str">
+      <c r="X10" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="X10" s="42" t="s">
-        <v>1787</v>
-      </c>
       <c r="Y10" s="42" t="s">
         <v>1787</v>
       </c>
       <c r="Z10" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA10" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AB10" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC10" s="42" t="s">
         <v>1560</v>
       </c>
-      <c r="AA10" s="59" t="s">
-        <v>1744</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -8069,42 +8110,48 @@
       <c r="Q11" s="58" t="s">
         <v>1746</v>
       </c>
-      <c r="R11" s="42" t="s">
+      <c r="R11" s="59" t="s">
+        <v>1747</v>
+      </c>
+      <c r="S11" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S11" s="40" t="str">
+      <c r="T11" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T11" s="40" t="str">
+      <c r="U11" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U11" s="58" t="str">
+      <c r="V11" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V11" s="42" t="s">
+      <c r="W11" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W11" s="68" t="str">
+      <c r="X11" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="X11" s="42" t="s">
-        <v>1787</v>
-      </c>
       <c r="Y11" s="42" t="s">
         <v>1787</v>
       </c>
       <c r="Z11" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA11" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AB11" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC11" s="42" t="s">
         <v>1561</v>
       </c>
-      <c r="AA11" s="59" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -8160,42 +8207,48 @@
       <c r="Q12" s="58" t="s">
         <v>1749</v>
       </c>
-      <c r="R12" s="42" t="s">
+      <c r="R12" s="59" t="s">
+        <v>1750</v>
+      </c>
+      <c r="S12" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S12" s="40" t="str">
+      <c r="T12" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T12" s="40" t="str">
+      <c r="U12" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U12" s="58" t="str">
+      <c r="V12" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V12" s="42" t="s">
+      <c r="W12" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W12" s="68" t="str">
+      <c r="X12" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-12</v>
       </c>
-      <c r="X12" s="42" t="s">
+      <c r="Y12" s="42" t="s">
         <v>1791</v>
       </c>
-      <c r="Y12" s="42" t="s">
+      <c r="Z12" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA12" s="42" t="s">
         <v>1798</v>
       </c>
-      <c r="Z12" s="42" t="s">
+      <c r="AB12" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC12" s="42" t="s">
         <v>1562</v>
       </c>
-      <c r="AA12" s="59" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -8251,42 +8304,48 @@
       <c r="Q13" s="58" t="s">
         <v>1752</v>
       </c>
-      <c r="R13" s="42" t="s">
+      <c r="R13" s="59" t="s">
+        <v>1753</v>
+      </c>
+      <c r="S13" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S13" s="40" t="str">
+      <c r="T13" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T13" s="40" t="str">
+      <c r="U13" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U13" s="58" t="str">
+      <c r="V13" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V13" s="42" t="s">
+      <c r="W13" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W13" s="68" t="str">
+      <c r="X13" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-13</v>
       </c>
-      <c r="X13" s="42" t="s">
+      <c r="Y13" s="42" t="s">
         <v>1791</v>
       </c>
-      <c r="Y13" s="42" t="s">
+      <c r="Z13" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA13" s="42" t="s">
         <v>1798</v>
       </c>
-      <c r="Z13" s="42" t="s">
+      <c r="AB13" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC13" s="42" t="s">
         <v>1563</v>
       </c>
-      <c r="AA13" s="59" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -8342,42 +8401,48 @@
       <c r="Q14" s="58" t="s">
         <v>1755</v>
       </c>
-      <c r="R14" s="42" t="s">
+      <c r="R14" s="59" t="s">
+        <v>1756</v>
+      </c>
+      <c r="S14" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="S14" s="40" t="str">
+      <c r="T14" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T14" s="40" t="str">
+      <c r="U14" s="40" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U14" s="58" t="str">
+      <c r="V14" s="58" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V14" s="42" t="s">
+      <c r="W14" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W14" s="68" t="str">
+      <c r="X14" s="68" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-14</v>
       </c>
-      <c r="X14" s="77" t="s">
+      <c r="Y14" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y14" s="78" t="s">
+      <c r="Z14" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA14" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z14" s="42" t="s">
+      <c r="AB14" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC14" s="42" t="s">
         <v>1475</v>
       </c>
-      <c r="AA14" s="59" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -8433,42 +8498,48 @@
       <c r="Q15" s="58" t="s">
         <v>1693</v>
       </c>
-      <c r="R15" s="40" t="s">
+      <c r="R15" s="58" t="s">
+        <v>1671</v>
+      </c>
+      <c r="S15" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S15" s="40" t="str">
-        <f t="shared" ref="S15" si="8">SUBSTITUTE(C15, "_", " ")</f>
+      <c r="T15" s="40" t="str">
+        <f t="shared" ref="T15" si="8">SUBSTITUTE(C15, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T15" s="40" t="str">
-        <f t="shared" ref="T15" si="9">SUBSTITUTE(D15, "_", " ")</f>
+      <c r="U15" s="40" t="str">
+        <f t="shared" ref="U15" si="9">SUBSTITUTE(D15, "_", " ")</f>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U15" s="58" t="str">
-        <f t="shared" ref="U15" si="10">SUBSTITUTE(E15, "_", " ")</f>
+      <c r="V15" s="58" t="str">
+        <f t="shared" ref="V15" si="10">SUBSTITUTE(E15, "_", " ")</f>
         <v>NBR.Informação</v>
       </c>
-      <c r="V15" s="42" t="s">
+      <c r="W15" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W15" s="67" t="str">
-        <f t="shared" ref="W15:W36" si="11">CONCATENATE("Key-ABNT-",A15)</f>
+      <c r="X15" s="67" t="str">
+        <f t="shared" ref="X15:X36" si="11">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
-      <c r="X15" s="77" t="s">
+      <c r="Y15" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y15" s="78" t="s">
+      <c r="Z15" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA15" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z15" s="63" t="s">
+      <c r="AB15" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC15" s="63" t="s">
         <v>1628</v>
       </c>
-      <c r="AA15" s="58" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -8524,42 +8595,48 @@
       <c r="Q16" s="58" t="s">
         <v>1694</v>
       </c>
-      <c r="R16" s="40" t="s">
+      <c r="R16" s="58" t="s">
+        <v>1672</v>
+      </c>
+      <c r="S16" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S16" s="40" t="str">
-        <f t="shared" ref="S16:S21" si="16">SUBSTITUTE(C16, "_", " ")</f>
+      <c r="T16" s="40" t="str">
+        <f t="shared" ref="T16:T21" si="16">SUBSTITUTE(C16, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T16" s="40" t="str">
-        <f t="shared" ref="T16:T21" si="17">SUBSTITUTE(D16, "_", " ")</f>
+      <c r="U16" s="40" t="str">
+        <f t="shared" ref="U16:U21" si="17">SUBSTITUTE(D16, "_", " ")</f>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U16" s="58" t="str">
-        <f t="shared" ref="U16:U21" si="18">SUBSTITUTE(E16, "_", " ")</f>
+      <c r="V16" s="58" t="str">
+        <f t="shared" ref="V16:V21" si="18">SUBSTITUTE(E16, "_", " ")</f>
         <v>NBR.Informação</v>
       </c>
-      <c r="V16" s="42" t="s">
+      <c r="W16" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W16" s="67" t="str">
+      <c r="X16" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="X16" s="77" t="s">
+      <c r="Y16" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y16" s="78" t="s">
+      <c r="Z16" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA16" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z16" s="63" t="s">
+      <c r="AB16" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC16" s="63" t="s">
         <v>1629</v>
       </c>
-      <c r="AA16" s="58" t="s">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -8615,42 +8692,48 @@
       <c r="Q17" s="58" t="s">
         <v>1695</v>
       </c>
-      <c r="R17" s="40" t="s">
+      <c r="R17" s="58" t="s">
+        <v>1673</v>
+      </c>
+      <c r="S17" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S17" s="40" t="str">
+      <c r="T17" s="40" t="str">
         <f t="shared" si="16"/>
         <v>Normativos</v>
       </c>
-      <c r="T17" s="40" t="str">
+      <c r="U17" s="40" t="str">
         <f t="shared" si="17"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U17" s="58" t="str">
+      <c r="V17" s="58" t="str">
         <f t="shared" si="18"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V17" s="42" t="s">
+      <c r="W17" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W17" s="67" t="str">
+      <c r="X17" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="X17" s="77" t="s">
+      <c r="Y17" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y17" s="78" t="s">
+      <c r="Z17" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA17" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z17" s="63" t="s">
+      <c r="AB17" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC17" s="63" t="s">
         <v>1630</v>
       </c>
-      <c r="AA17" s="58" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -8706,42 +8789,48 @@
       <c r="Q18" s="58" t="s">
         <v>1696</v>
       </c>
-      <c r="R18" s="40" t="s">
+      <c r="R18" s="58" t="s">
+        <v>1674</v>
+      </c>
+      <c r="S18" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S18" s="40" t="str">
+      <c r="T18" s="40" t="str">
         <f t="shared" si="16"/>
         <v>Normativos</v>
       </c>
-      <c r="T18" s="40" t="str">
+      <c r="U18" s="40" t="str">
         <f t="shared" si="17"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U18" s="58" t="str">
+      <c r="V18" s="58" t="str">
         <f t="shared" si="18"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V18" s="42" t="s">
+      <c r="W18" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W18" s="67" t="str">
+      <c r="X18" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="X18" s="77" t="s">
+      <c r="Y18" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y18" s="78" t="s">
+      <c r="Z18" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA18" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z18" s="63" t="s">
+      <c r="AB18" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC18" s="63" t="s">
         <v>1631</v>
       </c>
-      <c r="AA18" s="58" t="s">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -8797,42 +8886,48 @@
       <c r="Q19" s="58" t="s">
         <v>1697</v>
       </c>
-      <c r="R19" s="40" t="s">
+      <c r="R19" s="58" t="s">
+        <v>1675</v>
+      </c>
+      <c r="S19" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S19" s="40" t="str">
+      <c r="T19" s="40" t="str">
         <f t="shared" si="16"/>
         <v>Normativos</v>
       </c>
-      <c r="T19" s="40" t="str">
+      <c r="U19" s="40" t="str">
         <f t="shared" si="17"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U19" s="58" t="str">
+      <c r="V19" s="58" t="str">
         <f t="shared" si="18"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V19" s="42" t="s">
+      <c r="W19" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W19" s="67" t="str">
+      <c r="X19" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="X19" s="77" t="s">
+      <c r="Y19" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y19" s="78" t="s">
+      <c r="Z19" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA19" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z19" s="63" t="s">
+      <c r="AB19" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC19" s="63" t="s">
         <v>1632</v>
       </c>
-      <c r="AA19" s="58" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -8888,42 +8983,48 @@
       <c r="Q20" s="58" t="s">
         <v>1698</v>
       </c>
-      <c r="R20" s="40" t="s">
+      <c r="R20" s="58" t="s">
+        <v>1676</v>
+      </c>
+      <c r="S20" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S20" s="40" t="str">
+      <c r="T20" s="40" t="str">
         <f t="shared" si="16"/>
         <v>Normativos</v>
       </c>
-      <c r="T20" s="40" t="str">
+      <c r="U20" s="40" t="str">
         <f t="shared" si="17"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U20" s="58" t="str">
+      <c r="V20" s="58" t="str">
         <f t="shared" si="18"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V20" s="42" t="s">
+      <c r="W20" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W20" s="67" t="str">
+      <c r="X20" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="X20" s="77" t="s">
+      <c r="Y20" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y20" s="78" t="s">
+      <c r="Z20" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA20" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z20" s="63" t="s">
+      <c r="AB20" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC20" s="63" t="s">
         <v>1633</v>
       </c>
-      <c r="AA20" s="58" t="s">
-        <v>1676</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -8979,42 +9080,48 @@
       <c r="Q21" s="58" t="s">
         <v>1699</v>
       </c>
-      <c r="R21" s="40" t="s">
+      <c r="R21" s="58" t="s">
+        <v>1677</v>
+      </c>
+      <c r="S21" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S21" s="40" t="str">
+      <c r="T21" s="40" t="str">
         <f t="shared" si="16"/>
         <v>Normativos</v>
       </c>
-      <c r="T21" s="40" t="str">
+      <c r="U21" s="40" t="str">
         <f t="shared" si="17"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U21" s="58" t="str">
+      <c r="V21" s="58" t="str">
         <f t="shared" si="18"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V21" s="42" t="s">
+      <c r="W21" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W21" s="67" t="str">
+      <c r="X21" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="X21" s="77" t="s">
+      <c r="Y21" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y21" s="78" t="s">
+      <c r="Z21" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA21" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z21" s="63" t="s">
+      <c r="AB21" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC21" s="63" t="s">
         <v>1634</v>
       </c>
-      <c r="AA21" s="58" t="s">
-        <v>1677</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -9070,42 +9177,48 @@
       <c r="Q22" s="58" t="s">
         <v>1700</v>
       </c>
-      <c r="R22" s="40" t="s">
+      <c r="R22" s="58" t="s">
+        <v>1678</v>
+      </c>
+      <c r="S22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S22" s="40" t="str">
-        <f t="shared" ref="S22:S36" si="23">SUBSTITUTE(C22, "_", " ")</f>
+      <c r="T22" s="40" t="str">
+        <f t="shared" ref="T22:T36" si="23">SUBSTITUTE(C22, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T22" s="40" t="str">
-        <f t="shared" ref="T22:T36" si="24">SUBSTITUTE(D22, "_", " ")</f>
+      <c r="U22" s="40" t="str">
+        <f t="shared" ref="U22:U36" si="24">SUBSTITUTE(D22, "_", " ")</f>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U22" s="58" t="str">
-        <f t="shared" ref="U22:U36" si="25">SUBSTITUTE(E22, "_", " ")</f>
+      <c r="V22" s="58" t="str">
+        <f t="shared" ref="V22:V36" si="25">SUBSTITUTE(E22, "_", " ")</f>
         <v>NBR.Informação</v>
       </c>
-      <c r="V22" s="42" t="s">
+      <c r="W22" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W22" s="67" t="str">
+      <c r="X22" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="X22" s="77" t="s">
+      <c r="Y22" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y22" s="78" t="s">
+      <c r="Z22" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA22" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z22" s="63" t="s">
+      <c r="AB22" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC22" s="63" t="s">
         <v>1635</v>
       </c>
-      <c r="AA22" s="58" t="s">
-        <v>1678</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -9161,42 +9274,48 @@
       <c r="Q23" s="58" t="s">
         <v>1658</v>
       </c>
-      <c r="R23" s="40" t="s">
+      <c r="R23" s="58" t="s">
+        <v>1679</v>
+      </c>
+      <c r="S23" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S23" s="40" t="str">
+      <c r="T23" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T23" s="40" t="str">
+      <c r="U23" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U23" s="58" t="str">
+      <c r="V23" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V23" s="42" t="s">
+      <c r="W23" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W23" s="67" t="str">
+      <c r="X23" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-23</v>
       </c>
-      <c r="X23" s="77" t="s">
+      <c r="Y23" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y23" s="78" t="s">
+      <c r="Z23" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA23" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z23" s="63" t="s">
+      <c r="AB23" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC23" s="63" t="s">
         <v>1636</v>
       </c>
-      <c r="AA23" s="58" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -9252,42 +9371,48 @@
       <c r="Q24" s="58" t="s">
         <v>1701</v>
       </c>
-      <c r="R24" s="40" t="s">
+      <c r="R24" s="58" t="s">
+        <v>1680</v>
+      </c>
+      <c r="S24" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S24" s="40" t="str">
+      <c r="T24" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T24" s="40" t="str">
+      <c r="U24" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U24" s="58" t="str">
+      <c r="V24" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V24" s="42" t="s">
+      <c r="W24" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W24" s="67" t="str">
+      <c r="X24" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-24</v>
       </c>
-      <c r="X24" s="77" t="s">
+      <c r="Y24" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y24" s="78" t="s">
+      <c r="Z24" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA24" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z24" s="63" t="s">
+      <c r="AB24" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC24" s="63" t="s">
         <v>1637</v>
       </c>
-      <c r="AA24" s="58" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -9343,42 +9468,48 @@
       <c r="Q25" s="58" t="s">
         <v>1702</v>
       </c>
-      <c r="R25" s="40" t="s">
+      <c r="R25" s="58" t="s">
+        <v>1681</v>
+      </c>
+      <c r="S25" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S25" s="40" t="str">
+      <c r="T25" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T25" s="40" t="str">
+      <c r="U25" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U25" s="58" t="str">
+      <c r="V25" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V25" s="42" t="s">
+      <c r="W25" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W25" s="67" t="str">
+      <c r="X25" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-25</v>
       </c>
-      <c r="X25" s="77" t="s">
+      <c r="Y25" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y25" s="78" t="s">
+      <c r="Z25" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA25" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z25" s="63" t="s">
+      <c r="AB25" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC25" s="63" t="s">
         <v>1638</v>
       </c>
-      <c r="AA25" s="58" t="s">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -9434,42 +9565,48 @@
       <c r="Q26" s="58" t="s">
         <v>1703</v>
       </c>
-      <c r="R26" s="40" t="s">
+      <c r="R26" s="58" t="s">
+        <v>1682</v>
+      </c>
+      <c r="S26" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S26" s="40" t="str">
+      <c r="T26" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T26" s="40" t="str">
+      <c r="U26" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U26" s="58" t="str">
+      <c r="V26" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V26" s="42" t="s">
+      <c r="W26" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W26" s="67" t="str">
+      <c r="X26" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-26</v>
       </c>
-      <c r="X26" s="77" t="s">
+      <c r="Y26" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y26" s="78" t="s">
+      <c r="Z26" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA26" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z26" s="63" t="s">
+      <c r="AB26" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC26" s="63" t="s">
         <v>1639</v>
       </c>
-      <c r="AA26" s="58" t="s">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -9525,42 +9662,48 @@
       <c r="Q27" s="58" t="s">
         <v>1704</v>
       </c>
-      <c r="R27" s="40" t="s">
+      <c r="R27" s="58" t="s">
+        <v>1683</v>
+      </c>
+      <c r="S27" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S27" s="40" t="str">
+      <c r="T27" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T27" s="40" t="str">
+      <c r="U27" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U27" s="58" t="str">
+      <c r="V27" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V27" s="42" t="s">
+      <c r="W27" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W27" s="67" t="str">
+      <c r="X27" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-27</v>
       </c>
-      <c r="X27" s="77" t="s">
+      <c r="Y27" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y27" s="78" t="s">
+      <c r="Z27" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA27" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z27" s="63" t="s">
+      <c r="AB27" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC27" s="63" t="s">
         <v>1640</v>
       </c>
-      <c r="AA27" s="58" t="s">
-        <v>1683</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -9616,42 +9759,48 @@
       <c r="Q28" s="58" t="s">
         <v>1705</v>
       </c>
-      <c r="R28" s="40" t="s">
+      <c r="R28" s="58" t="s">
+        <v>1684</v>
+      </c>
+      <c r="S28" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S28" s="40" t="str">
+      <c r="T28" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T28" s="40" t="str">
+      <c r="U28" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U28" s="58" t="str">
+      <c r="V28" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V28" s="42" t="s">
+      <c r="W28" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W28" s="67" t="str">
+      <c r="X28" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-28</v>
       </c>
-      <c r="X28" s="77" t="s">
+      <c r="Y28" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y28" s="78" t="s">
+      <c r="Z28" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA28" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z28" s="63" t="s">
+      <c r="AB28" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC28" s="63" t="s">
         <v>1641</v>
       </c>
-      <c r="AA28" s="58" t="s">
-        <v>1684</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -9707,42 +9856,48 @@
       <c r="Q29" s="58" t="s">
         <v>1706</v>
       </c>
-      <c r="R29" s="40" t="s">
+      <c r="R29" s="58" t="s">
+        <v>1685</v>
+      </c>
+      <c r="S29" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S29" s="40" t="str">
+      <c r="T29" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T29" s="40" t="str">
+      <c r="U29" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U29" s="58" t="str">
+      <c r="V29" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V29" s="42" t="s">
+      <c r="W29" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W29" s="67" t="str">
+      <c r="X29" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-29</v>
       </c>
-      <c r="X29" s="77" t="s">
+      <c r="Y29" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y29" s="78" t="s">
+      <c r="Z29" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA29" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z29" s="63" t="s">
+      <c r="AB29" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC29" s="63" t="s">
         <v>1642</v>
       </c>
-      <c r="AA29" s="58" t="s">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -9798,42 +9953,48 @@
       <c r="Q30" s="58" t="s">
         <v>1707</v>
       </c>
-      <c r="R30" s="40" t="s">
+      <c r="R30" s="58" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S30" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S30" s="40" t="str">
+      <c r="T30" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T30" s="40" t="str">
+      <c r="U30" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U30" s="58" t="str">
+      <c r="V30" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V30" s="42" t="s">
+      <c r="W30" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W30" s="67" t="str">
+      <c r="X30" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-30</v>
       </c>
-      <c r="X30" s="77" t="s">
+      <c r="Y30" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y30" s="78" t="s">
+      <c r="Z30" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA30" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z30" s="63" t="s">
+      <c r="AB30" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC30" s="63" t="s">
         <v>1643</v>
       </c>
-      <c r="AA30" s="58" t="s">
-        <v>1686</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="56">
         <v>31</v>
       </c>
@@ -9889,42 +10050,48 @@
       <c r="Q31" s="58" t="s">
         <v>1708</v>
       </c>
-      <c r="R31" s="40" t="s">
+      <c r="R31" s="58" t="s">
+        <v>1687</v>
+      </c>
+      <c r="S31" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S31" s="40" t="str">
+      <c r="T31" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T31" s="40" t="str">
+      <c r="U31" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U31" s="58" t="str">
+      <c r="V31" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V31" s="42" t="s">
+      <c r="W31" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W31" s="67" t="str">
+      <c r="X31" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-31</v>
       </c>
-      <c r="X31" s="77" t="s">
+      <c r="Y31" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y31" s="78" t="s">
+      <c r="Z31" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA31" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z31" s="63" t="s">
+      <c r="AB31" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC31" s="63" t="s">
         <v>1644</v>
       </c>
-      <c r="AA31" s="58" t="s">
-        <v>1687</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="56">
         <v>32</v>
       </c>
@@ -9980,42 +10147,48 @@
       <c r="Q32" s="58" t="s">
         <v>1709</v>
       </c>
-      <c r="R32" s="40" t="s">
+      <c r="R32" s="58" t="s">
+        <v>1688</v>
+      </c>
+      <c r="S32" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S32" s="40" t="str">
+      <c r="T32" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T32" s="40" t="str">
+      <c r="U32" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U32" s="58" t="str">
+      <c r="V32" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V32" s="42" t="s">
+      <c r="W32" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W32" s="67" t="str">
+      <c r="X32" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-32</v>
       </c>
-      <c r="X32" s="77" t="s">
+      <c r="Y32" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y32" s="78" t="s">
+      <c r="Z32" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA32" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z32" s="63" t="s">
+      <c r="AB32" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC32" s="63" t="s">
         <v>1645</v>
       </c>
-      <c r="AA32" s="58" t="s">
-        <v>1688</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="56">
         <v>33</v>
       </c>
@@ -10071,42 +10244,48 @@
       <c r="Q33" s="58" t="s">
         <v>1710</v>
       </c>
-      <c r="R33" s="40" t="s">
+      <c r="R33" s="58" t="s">
+        <v>1689</v>
+      </c>
+      <c r="S33" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S33" s="40" t="str">
+      <c r="T33" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T33" s="40" t="str">
+      <c r="U33" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U33" s="58" t="str">
+      <c r="V33" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V33" s="42" t="s">
+      <c r="W33" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W33" s="67" t="str">
+      <c r="X33" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-33</v>
       </c>
-      <c r="X33" s="77" t="s">
+      <c r="Y33" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y33" s="78" t="s">
+      <c r="Z33" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA33" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z33" s="63" t="s">
+      <c r="AB33" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC33" s="63" t="s">
         <v>1646</v>
       </c>
-      <c r="AA33" s="58" t="s">
-        <v>1689</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="56">
         <v>34</v>
       </c>
@@ -10162,42 +10341,48 @@
       <c r="Q34" s="58" t="s">
         <v>1711</v>
       </c>
-      <c r="R34" s="40" t="s">
+      <c r="R34" s="58" t="s">
+        <v>1690</v>
+      </c>
+      <c r="S34" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S34" s="40" t="str">
+      <c r="T34" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T34" s="40" t="str">
+      <c r="U34" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U34" s="58" t="str">
+      <c r="V34" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V34" s="42" t="s">
+      <c r="W34" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W34" s="67" t="str">
+      <c r="X34" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-34</v>
       </c>
-      <c r="X34" s="77" t="s">
+      <c r="Y34" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y34" s="78" t="s">
+      <c r="Z34" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA34" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z34" s="63" t="s">
+      <c r="AB34" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC34" s="63" t="s">
         <v>1647</v>
       </c>
-      <c r="AA34" s="58" t="s">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="56">
         <v>35</v>
       </c>
@@ -10253,42 +10438,48 @@
       <c r="Q35" s="58" t="s">
         <v>1712</v>
       </c>
-      <c r="R35" s="40" t="s">
+      <c r="R35" s="58" t="s">
+        <v>1691</v>
+      </c>
+      <c r="S35" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S35" s="40" t="str">
+      <c r="T35" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T35" s="40" t="str">
+      <c r="U35" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U35" s="58" t="str">
+      <c r="V35" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V35" s="42" t="s">
+      <c r="W35" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W35" s="67" t="str">
+      <c r="X35" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-35</v>
       </c>
-      <c r="X35" s="77" t="s">
+      <c r="Y35" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y35" s="78" t="s">
+      <c r="Z35" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA35" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z35" s="63" t="s">
+      <c r="AB35" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC35" s="63" t="s">
         <v>1648</v>
       </c>
-      <c r="AA35" s="58" t="s">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="56">
         <v>36</v>
       </c>
@@ -10344,65 +10535,66 @@
       <c r="Q36" s="58" t="s">
         <v>1713</v>
       </c>
-      <c r="R36" s="40" t="s">
+      <c r="R36" s="58" t="s">
+        <v>1692</v>
+      </c>
+      <c r="S36" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="S36" s="40" t="str">
+      <c r="T36" s="40" t="str">
         <f t="shared" si="23"/>
         <v>Normativos</v>
       </c>
-      <c r="T36" s="40" t="str">
+      <c r="U36" s="40" t="str">
         <f t="shared" si="24"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U36" s="58" t="str">
+      <c r="V36" s="58" t="str">
         <f t="shared" si="25"/>
         <v>NBR.Informação</v>
       </c>
-      <c r="V36" s="42" t="s">
+      <c r="W36" s="42" t="s">
         <v>1551</v>
       </c>
-      <c r="W36" s="67" t="str">
+      <c r="X36" s="67" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-36</v>
       </c>
-      <c r="X36" s="77" t="s">
+      <c r="Y36" s="77" t="s">
         <v>1793</v>
       </c>
-      <c r="Y36" s="78" t="s">
+      <c r="Z36" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AA36" s="78" t="s">
         <v>1792</v>
       </c>
-      <c r="Z36" s="63" t="s">
+      <c r="AB36" s="42" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC36" s="63" t="s">
         <v>1649</v>
       </c>
-      <c r="AA36" s="58" t="s">
-        <v>1692</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Z15:Z36">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+  <conditionalFormatting sqref="F2:F14">
+    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 A15:B36">
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  <conditionalFormatting sqref="AC15:AC36">
+    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA14 A2:B14">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B36">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y2">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R14">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10417,13 +10609,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1AA270-C700-44D7-AFAB-8480CF5F2B6E}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
         <v>1483</v>
       </c>
@@ -10488,7 +10680,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -10555,7 +10747,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10570,14 +10762,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBE7ADA-121D-48D5-88A4-2E192550983E}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.69921875" customWidth="1"/>
-    <col min="3" max="3" width="16.69921875" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -10588,7 +10780,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -10601,7 +10793,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10613,39 +10805,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AA732"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.796875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.796875" style="9" customWidth="1"/>
-    <col min="11" max="11" width="16.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.83203125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.83203125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23.5" style="9" customWidth="1"/>
     <col min="14" max="14" width="6" style="9" customWidth="1"/>
-    <col min="15" max="15" width="45.69921875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.69921875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="45.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.796875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="22.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.796875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="14.69921875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.83203125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.83203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="14.6640625" style="1" customWidth="1"/>
     <col min="26" max="26" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.19921875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="11.1640625" style="1" customWidth="1"/>
     <col min="28" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>31</v>
       </c>
@@ -10728,7 +10920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -10811,7 +11003,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -10894,7 +11086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -10977,7 +11169,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>5</v>
       </c>
@@ -11060,7 +11252,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>6</v>
       </c>
@@ -11143,7 +11335,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>7</v>
       </c>
@@ -11226,7 +11418,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>8</v>
       </c>
@@ -11309,7 +11501,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>9</v>
       </c>
@@ -11392,7 +11584,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>10</v>
       </c>
@@ -11475,7 +11667,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>11</v>
       </c>
@@ -11558,7 +11750,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>12</v>
       </c>
@@ -11641,7 +11833,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>13</v>
       </c>
@@ -11724,7 +11916,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>14</v>
       </c>
@@ -11807,7 +11999,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>15</v>
       </c>
@@ -11890,7 +12082,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>16</v>
       </c>
@@ -11973,7 +12165,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>17</v>
       </c>
@@ -12056,7 +12248,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>18</v>
       </c>
@@ -12139,7 +12331,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>19</v>
       </c>
@@ -12222,7 +12414,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>20</v>
       </c>
@@ -12305,7 +12497,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>21</v>
       </c>
@@ -12388,7 +12580,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>22</v>
       </c>
@@ -12471,7 +12663,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>23</v>
       </c>
@@ -12554,7 +12746,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>24</v>
       </c>
@@ -12637,7 +12829,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>25</v>
       </c>
@@ -12720,7 +12912,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>26</v>
       </c>
@@ -12803,7 +12995,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>27</v>
       </c>
@@ -12886,7 +13078,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>28</v>
       </c>
@@ -12969,7 +13161,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>29</v>
       </c>
@@ -13052,7 +13244,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>30</v>
       </c>
@@ -13135,7 +13327,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>31</v>
       </c>
@@ -13218,7 +13410,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>32</v>
       </c>
@@ -13301,7 +13493,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>33</v>
       </c>
@@ -13384,7 +13576,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>34</v>
       </c>
@@ -13467,7 +13659,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>35</v>
       </c>
@@ -13550,7 +13742,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>36</v>
       </c>
@@ -13633,7 +13825,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>37</v>
       </c>
@@ -13716,7 +13908,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>38</v>
       </c>
@@ -13799,7 +13991,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>39</v>
       </c>
@@ -13882,7 +14074,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>40</v>
       </c>
@@ -13965,7 +14157,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>41</v>
       </c>
@@ -14048,7 +14240,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>42</v>
       </c>
@@ -14131,7 +14323,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>43</v>
       </c>
@@ -14214,7 +14406,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>44</v>
       </c>
@@ -14297,7 +14489,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>45</v>
       </c>
@@ -14380,7 +14572,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46</v>
       </c>
@@ -14463,7 +14655,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>47</v>
       </c>
@@ -14546,7 +14738,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>48</v>
       </c>
@@ -14629,7 +14821,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>49</v>
       </c>
@@ -14712,7 +14904,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>50</v>
       </c>
@@ -14795,7 +14987,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>51</v>
       </c>
@@ -14878,7 +15070,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>52</v>
       </c>
@@ -14961,7 +15153,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>53</v>
       </c>
@@ -15044,7 +15236,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>54</v>
       </c>
@@ -15127,7 +15319,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>55</v>
       </c>
@@ -15210,7 +15402,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>56</v>
       </c>
@@ -15293,7 +15485,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>57</v>
       </c>
@@ -15376,7 +15568,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>58</v>
       </c>
@@ -15459,7 +15651,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>59</v>
       </c>
@@ -15542,7 +15734,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>60</v>
       </c>
@@ -15625,7 +15817,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>61</v>
       </c>
@@ -15708,7 +15900,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>62</v>
       </c>
@@ -15791,7 +15983,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>63</v>
       </c>
@@ -15874,7 +16066,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>64</v>
       </c>
@@ -15957,7 +16149,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>65</v>
       </c>
@@ -16040,7 +16232,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>66</v>
       </c>
@@ -16123,7 +16315,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>67</v>
       </c>
@@ -16206,7 +16398,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>68</v>
       </c>
@@ -16289,7 +16481,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>69</v>
       </c>
@@ -16372,7 +16564,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>70</v>
       </c>
@@ -16455,7 +16647,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>71</v>
       </c>
@@ -16538,7 +16730,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>72</v>
       </c>
@@ -16621,7 +16813,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>73</v>
       </c>
@@ -16704,7 +16896,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>74</v>
       </c>
@@ -16787,7 +16979,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>75</v>
       </c>
@@ -16870,7 +17062,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>76</v>
       </c>
@@ -16953,7 +17145,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>77</v>
       </c>
@@ -17036,7 +17228,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>78</v>
       </c>
@@ -17119,7 +17311,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>79</v>
       </c>
@@ -17202,7 +17394,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>80</v>
       </c>
@@ -17285,7 +17477,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>81</v>
       </c>
@@ -17368,7 +17560,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>82</v>
       </c>
@@ -17451,7 +17643,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>83</v>
       </c>
@@ -17534,7 +17726,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>84</v>
       </c>
@@ -17617,7 +17809,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>85</v>
       </c>
@@ -17700,7 +17892,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>86</v>
       </c>
@@ -17783,7 +17975,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>87</v>
       </c>
@@ -17866,7 +18058,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>88</v>
       </c>
@@ -17949,7 +18141,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>89</v>
       </c>
@@ -18032,7 +18224,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>90</v>
       </c>
@@ -18115,7 +18307,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>91</v>
       </c>
@@ -18198,7 +18390,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>92</v>
       </c>
@@ -18281,7 +18473,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>93</v>
       </c>
@@ -18364,7 +18556,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>94</v>
       </c>
@@ -18447,7 +18639,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>95</v>
       </c>
@@ -18530,7 +18722,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>96</v>
       </c>
@@ -18613,7 +18805,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>97</v>
       </c>
@@ -18696,7 +18888,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>98</v>
       </c>
@@ -18779,7 +18971,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>99</v>
       </c>
@@ -18862,7 +19054,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>100</v>
       </c>
@@ -18945,7 +19137,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>101</v>
       </c>
@@ -19028,7 +19220,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>102</v>
       </c>
@@ -19111,7 +19303,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>103</v>
       </c>
@@ -19194,7 +19386,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>104</v>
       </c>
@@ -19277,7 +19469,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>105</v>
       </c>
@@ -19360,7 +19552,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>106</v>
       </c>
@@ -19443,7 +19635,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>107</v>
       </c>
@@ -19526,7 +19718,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>108</v>
       </c>
@@ -19609,7 +19801,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>109</v>
       </c>
@@ -19692,7 +19884,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>110</v>
       </c>
@@ -19775,7 +19967,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>111</v>
       </c>
@@ -19858,7 +20050,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>112</v>
       </c>
@@ -19941,7 +20133,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>113</v>
       </c>
@@ -20024,7 +20216,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>114</v>
       </c>
@@ -20107,7 +20299,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>115</v>
       </c>
@@ -20190,7 +20382,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>116</v>
       </c>
@@ -20273,7 +20465,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>117</v>
       </c>
@@ -20356,7 +20548,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>118</v>
       </c>
@@ -20439,7 +20631,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>119</v>
       </c>
@@ -20522,7 +20714,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>120</v>
       </c>
@@ -20605,7 +20797,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>121</v>
       </c>
@@ -20688,7 +20880,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>122</v>
       </c>
@@ -20771,7 +20963,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>123</v>
       </c>
@@ -20854,7 +21046,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>124</v>
       </c>
@@ -20937,7 +21129,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>125</v>
       </c>
@@ -21020,7 +21212,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>126</v>
       </c>
@@ -21103,7 +21295,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>127</v>
       </c>
@@ -21186,7 +21378,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>128</v>
       </c>
@@ -21269,7 +21461,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>129</v>
       </c>
@@ -21352,7 +21544,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>130</v>
       </c>
@@ -21435,7 +21627,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>131</v>
       </c>
@@ -21518,7 +21710,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>132</v>
       </c>
@@ -21601,7 +21793,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>133</v>
       </c>
@@ -21684,7 +21876,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>134</v>
       </c>
@@ -21767,7 +21959,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>135</v>
       </c>
@@ -21850,7 +22042,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>136</v>
       </c>
@@ -21933,7 +22125,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>137</v>
       </c>
@@ -22016,7 +22208,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>138</v>
       </c>
@@ -22099,7 +22291,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>139</v>
       </c>
@@ -22182,7 +22374,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>140</v>
       </c>
@@ -22265,7 +22457,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>141</v>
       </c>
@@ -22348,7 +22540,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>142</v>
       </c>
@@ -22431,7 +22623,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>143</v>
       </c>
@@ -22514,7 +22706,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>144</v>
       </c>
@@ -22597,7 +22789,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>145</v>
       </c>
@@ -22680,7 +22872,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>146</v>
       </c>
@@ -22763,7 +22955,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>147</v>
       </c>
@@ -22846,7 +23038,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>148</v>
       </c>
@@ -22929,7 +23121,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>149</v>
       </c>
@@ -23012,7 +23204,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>150</v>
       </c>
@@ -23095,7 +23287,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>151</v>
       </c>
@@ -23178,7 +23370,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>152</v>
       </c>
@@ -23261,7 +23453,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>153</v>
       </c>
@@ -23344,7 +23536,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="12">
         <v>154</v>
       </c>
@@ -23427,7 +23619,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>155</v>
       </c>
@@ -23510,7 +23702,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="12">
         <v>156</v>
       </c>
@@ -23593,7 +23785,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>157</v>
       </c>
@@ -23676,7 +23868,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="12">
         <v>158</v>
       </c>
@@ -23759,7 +23951,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>159</v>
       </c>
@@ -23842,7 +24034,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="12">
         <v>160</v>
       </c>
@@ -23925,7 +24117,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>161</v>
       </c>
@@ -24008,7 +24200,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="12">
         <v>162</v>
       </c>
@@ -24091,7 +24283,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>163</v>
       </c>
@@ -24174,7 +24366,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="12">
         <v>164</v>
       </c>
@@ -24257,7 +24449,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="165" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>165</v>
       </c>
@@ -24340,7 +24532,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="12">
         <v>166</v>
       </c>
@@ -24423,7 +24615,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>167</v>
       </c>
@@ -24506,7 +24698,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="168" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="12">
         <v>168</v>
       </c>
@@ -24589,7 +24781,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="12">
         <v>169</v>
       </c>
@@ -24672,7 +24864,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="170" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="12">
         <v>170</v>
       </c>
@@ -24755,7 +24947,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="12">
         <v>171</v>
       </c>
@@ -24838,7 +25030,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="172" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="12">
         <v>172</v>
       </c>
@@ -24921,7 +25113,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="12">
         <v>173</v>
       </c>
@@ -25004,7 +25196,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="12">
         <v>174</v>
       </c>
@@ -25087,7 +25279,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="175" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="12">
         <v>175</v>
       </c>
@@ -25170,7 +25362,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="12">
         <v>176</v>
       </c>
@@ -25253,7 +25445,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="12">
         <v>177</v>
       </c>
@@ -25336,7 +25528,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="12">
         <v>178</v>
       </c>
@@ -25419,7 +25611,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="12">
         <v>179</v>
       </c>
@@ -25502,7 +25694,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="12">
         <v>180</v>
       </c>
@@ -25585,7 +25777,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="12">
         <v>181</v>
       </c>
@@ -25668,7 +25860,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="12">
         <v>182</v>
       </c>
@@ -25751,7 +25943,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="12">
         <v>183</v>
       </c>
@@ -25834,7 +26026,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="184" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="12">
         <v>184</v>
       </c>
@@ -25917,7 +26109,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="185" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="12">
         <v>185</v>
       </c>
@@ -26000,7 +26192,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="12">
         <v>186</v>
       </c>
@@ -26083,7 +26275,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="12">
         <v>187</v>
       </c>
@@ -26166,7 +26358,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="12">
         <v>188</v>
       </c>
@@ -26249,7 +26441,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="189" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="12">
         <v>189</v>
       </c>
@@ -26332,7 +26524,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="12">
         <v>190</v>
       </c>
@@ -26415,7 +26607,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="12">
         <v>191</v>
       </c>
@@ -26498,7 +26690,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="192" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="12">
         <v>192</v>
       </c>
@@ -26581,7 +26773,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="193" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="12">
         <v>193</v>
       </c>
@@ -26664,7 +26856,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="12">
         <v>194</v>
       </c>
@@ -26747,7 +26939,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="12">
         <v>195</v>
       </c>
@@ -26830,7 +27022,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="12">
         <v>196</v>
       </c>
@@ -26913,7 +27105,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="197" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="12">
         <v>197</v>
       </c>
@@ -26996,7 +27188,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="198" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="12">
         <v>198</v>
       </c>
@@ -27079,7 +27271,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="199" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="12">
         <v>199</v>
       </c>
@@ -27162,7 +27354,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="200" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="12">
         <v>200</v>
       </c>
@@ -27245,7 +27437,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="12">
         <v>201</v>
       </c>
@@ -27328,7 +27520,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="202" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="12">
         <v>202</v>
       </c>
@@ -27411,7 +27603,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="12">
         <v>203</v>
       </c>
@@ -27494,7 +27686,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="204" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="12">
         <v>204</v>
       </c>
@@ -27577,7 +27769,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="205" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="12">
         <v>205</v>
       </c>
@@ -27660,7 +27852,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="206" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="12">
         <v>206</v>
       </c>
@@ -27743,7 +27935,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="12">
         <v>207</v>
       </c>
@@ -27826,7 +28018,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="12">
         <v>208</v>
       </c>
@@ -27909,7 +28101,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="209" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="12">
         <v>209</v>
       </c>
@@ -27992,7 +28184,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="210" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="12">
         <v>210</v>
       </c>
@@ -28075,7 +28267,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="12">
         <v>211</v>
       </c>
@@ -28158,7 +28350,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="212" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="12">
         <v>212</v>
       </c>
@@ -28241,7 +28433,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="213" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="12">
         <v>213</v>
       </c>
@@ -28324,7 +28516,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="214" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="12">
         <v>214</v>
       </c>
@@ -28407,7 +28599,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="215" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="12">
         <v>215</v>
       </c>
@@ -28490,7 +28682,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="216" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="12">
         <v>216</v>
       </c>
@@ -28573,7 +28765,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="217" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="12">
         <v>217</v>
       </c>
@@ -28656,7 +28848,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="218" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="12">
         <v>218</v>
       </c>
@@ -28739,7 +28931,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="219" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="12">
         <v>219</v>
       </c>
@@ -28822,7 +29014,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="220" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="12">
         <v>220</v>
       </c>
@@ -28905,7 +29097,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="221" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="12">
         <v>221</v>
       </c>
@@ -28988,7 +29180,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="222" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="12">
         <v>222</v>
       </c>
@@ -29071,7 +29263,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="223" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="12">
         <v>223</v>
       </c>
@@ -29154,7 +29346,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="224" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="12">
         <v>224</v>
       </c>
@@ -29237,7 +29429,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="225" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="12">
         <v>225</v>
       </c>
@@ -29320,7 +29512,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="226" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="12">
         <v>226</v>
       </c>
@@ -29403,7 +29595,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="227" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="12">
         <v>227</v>
       </c>
@@ -29486,7 +29678,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="228" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="12">
         <v>228</v>
       </c>
@@ -29569,7 +29761,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="229" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="12">
         <v>229</v>
       </c>
@@ -29652,7 +29844,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="230" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="12">
         <v>230</v>
       </c>
@@ -29735,7 +29927,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="231" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="12">
         <v>231</v>
       </c>
@@ -29818,7 +30010,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="232" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="12">
         <v>232</v>
       </c>
@@ -29901,7 +30093,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="233" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="12">
         <v>233</v>
       </c>
@@ -29984,7 +30176,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="234" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="12">
         <v>234</v>
       </c>
@@ -30067,7 +30259,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="235" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="12">
         <v>235</v>
       </c>
@@ -30150,7 +30342,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="236" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="12">
         <v>236</v>
       </c>
@@ -30233,7 +30425,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="237" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="12">
         <v>237</v>
       </c>
@@ -30316,7 +30508,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="238" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="12">
         <v>238</v>
       </c>
@@ -30399,7 +30591,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="239" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="12">
         <v>239</v>
       </c>
@@ -30482,7 +30674,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="240" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="12">
         <v>240</v>
       </c>
@@ -30565,7 +30757,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="241" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="12">
         <v>241</v>
       </c>
@@ -30648,7 +30840,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="242" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="12">
         <v>242</v>
       </c>
@@ -30731,7 +30923,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="243" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="12">
         <v>243</v>
       </c>
@@ -30814,7 +31006,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="244" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="12">
         <v>244</v>
       </c>
@@ -30897,7 +31089,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="245" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="12">
         <v>245</v>
       </c>
@@ -30980,7 +31172,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="246" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="12">
         <v>246</v>
       </c>
@@ -31063,7 +31255,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="247" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="12">
         <v>247</v>
       </c>
@@ -31146,7 +31338,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="248" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="12">
         <v>248</v>
       </c>
@@ -31229,7 +31421,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="249" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="12">
         <v>249</v>
       </c>
@@ -31312,7 +31504,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="250" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="12">
         <v>250</v>
       </c>
@@ -31395,7 +31587,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="251" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="12">
         <v>251</v>
       </c>
@@ -31478,7 +31670,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="252" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="12">
         <v>252</v>
       </c>
@@ -31561,7 +31753,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="253" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="12">
         <v>253</v>
       </c>
@@ -31644,7 +31836,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="254" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="12">
         <v>254</v>
       </c>
@@ -31727,7 +31919,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="255" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="12">
         <v>255</v>
       </c>
@@ -31810,7 +32002,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="256" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="12">
         <v>256</v>
       </c>
@@ -31893,7 +32085,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="257" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="12">
         <v>257</v>
       </c>
@@ -31976,7 +32168,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="258" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="12">
         <v>258</v>
       </c>
@@ -32059,7 +32251,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="259" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="12">
         <v>259</v>
       </c>
@@ -32142,7 +32334,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="260" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="12">
         <v>260</v>
       </c>
@@ -32225,7 +32417,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="261" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="12">
         <v>261</v>
       </c>
@@ -32308,7 +32500,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="262" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="12">
         <v>262</v>
       </c>
@@ -32391,7 +32583,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="263" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="12">
         <v>263</v>
       </c>
@@ -32474,7 +32666,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="264" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="12">
         <v>264</v>
       </c>
@@ -32557,7 +32749,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="265" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="12">
         <v>265</v>
       </c>
@@ -32640,7 +32832,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="266" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="12">
         <v>266</v>
       </c>
@@ -32723,7 +32915,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="267" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="12">
         <v>267</v>
       </c>
@@ -32806,7 +32998,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="268" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="12">
         <v>268</v>
       </c>
@@ -32889,7 +33081,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="269" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="12">
         <v>269</v>
       </c>
@@ -32972,7 +33164,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="270" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="12">
         <v>270</v>
       </c>
@@ -33055,7 +33247,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="271" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="12">
         <v>271</v>
       </c>
@@ -33138,7 +33330,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="272" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="12">
         <v>272</v>
       </c>
@@ -33221,7 +33413,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="273" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="12">
         <v>273</v>
       </c>
@@ -33304,7 +33496,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="274" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="12">
         <v>274</v>
       </c>
@@ -33387,7 +33579,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="275" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="12">
         <v>275</v>
       </c>
@@ -33470,7 +33662,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="276" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="12">
         <v>276</v>
       </c>
@@ -33553,7 +33745,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="277" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="12">
         <v>277</v>
       </c>
@@ -33636,7 +33828,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="278" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="12">
         <v>278</v>
       </c>
@@ -33719,7 +33911,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="279" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="12">
         <v>279</v>
       </c>
@@ -33802,7 +33994,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="280" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="12">
         <v>280</v>
       </c>
@@ -33885,7 +34077,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="281" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="12">
         <v>281</v>
       </c>
@@ -33968,7 +34160,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="282" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="12">
         <v>282</v>
       </c>
@@ -34051,7 +34243,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="283" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="12">
         <v>283</v>
       </c>
@@ -34134,7 +34326,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="284" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="12">
         <v>284</v>
       </c>
@@ -34217,7 +34409,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="285" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="12">
         <v>285</v>
       </c>
@@ -34300,7 +34492,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="286" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="12">
         <v>286</v>
       </c>
@@ -34383,7 +34575,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="287" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="12">
         <v>287</v>
       </c>
@@ -34466,7 +34658,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="288" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="12">
         <v>288</v>
       </c>
@@ -34549,7 +34741,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="289" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="12">
         <v>289</v>
       </c>
@@ -34632,7 +34824,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="290" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="12">
         <v>290</v>
       </c>
@@ -34715,7 +34907,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="291" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="12">
         <v>291</v>
       </c>
@@ -34798,7 +34990,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="292" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="12">
         <v>292</v>
       </c>
@@ -34881,7 +35073,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="293" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="12">
         <v>293</v>
       </c>
@@ -34964,7 +35156,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="294" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="12">
         <v>294</v>
       </c>
@@ -35047,7 +35239,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="295" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="12">
         <v>295</v>
       </c>
@@ -35130,7 +35322,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="296" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="12">
         <v>296</v>
       </c>
@@ -35213,7 +35405,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="297" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="12">
         <v>297</v>
       </c>
@@ -35296,7 +35488,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="298" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="12">
         <v>298</v>
       </c>
@@ -35379,7 +35571,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="299" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="12">
         <v>299</v>
       </c>
@@ -35462,7 +35654,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="300" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="12">
         <v>300</v>
       </c>
@@ -35545,7 +35737,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="301" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="12">
         <v>301</v>
       </c>
@@ -35628,7 +35820,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="302" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="12">
         <v>302</v>
       </c>
@@ -35711,7 +35903,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="303" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="12">
         <v>303</v>
       </c>
@@ -35794,7 +35986,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="304" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="12">
         <v>304</v>
       </c>
@@ -35877,7 +36069,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="305" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="12">
         <v>305</v>
       </c>
@@ -35960,7 +36152,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="306" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="12">
         <v>306</v>
       </c>
@@ -36043,7 +36235,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="307" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="12">
         <v>307</v>
       </c>
@@ -36126,7 +36318,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="308" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="12">
         <v>308</v>
       </c>
@@ -36209,7 +36401,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="309" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="12">
         <v>309</v>
       </c>
@@ -36292,7 +36484,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="310" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="12">
         <v>310</v>
       </c>
@@ -36375,7 +36567,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="311" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="12">
         <v>311</v>
       </c>
@@ -36458,7 +36650,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="312" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="12">
         <v>312</v>
       </c>
@@ -36541,7 +36733,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="313" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="12">
         <v>313</v>
       </c>
@@ -36624,7 +36816,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="314" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="12">
         <v>314</v>
       </c>
@@ -36707,7 +36899,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="315" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="12">
         <v>315</v>
       </c>
@@ -36790,7 +36982,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="316" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="12">
         <v>316</v>
       </c>
@@ -36873,7 +37065,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="317" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="12">
         <v>317</v>
       </c>
@@ -36956,7 +37148,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="318" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="12">
         <v>318</v>
       </c>
@@ -37039,7 +37231,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="319" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="12">
         <v>319</v>
       </c>
@@ -37122,7 +37314,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="320" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="12">
         <v>320</v>
       </c>
@@ -37205,7 +37397,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="321" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="12">
         <v>321</v>
       </c>
@@ -37288,7 +37480,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="322" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="12">
         <v>322</v>
       </c>
@@ -37371,7 +37563,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="323" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="12">
         <v>323</v>
       </c>
@@ -37454,7 +37646,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="324" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="12">
         <v>324</v>
       </c>
@@ -37537,7 +37729,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="325" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="12">
         <v>325</v>
       </c>
@@ -37620,7 +37812,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="326" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="12">
         <v>326</v>
       </c>
@@ -37703,7 +37895,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="327" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="12">
         <v>327</v>
       </c>
@@ -37786,7 +37978,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="328" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="12">
         <v>328</v>
       </c>
@@ -37869,7 +38061,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="329" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="12">
         <v>329</v>
       </c>
@@ -37952,7 +38144,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="330" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="12">
         <v>330</v>
       </c>
@@ -38035,7 +38227,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="331" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="12">
         <v>331</v>
       </c>
@@ -38118,7 +38310,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="332" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="12">
         <v>332</v>
       </c>
@@ -38201,7 +38393,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="333" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="12">
         <v>333</v>
       </c>
@@ -38284,7 +38476,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="334" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="12">
         <v>334</v>
       </c>
@@ -38367,7 +38559,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="335" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="12">
         <v>335</v>
       </c>
@@ -38450,7 +38642,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="336" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="12">
         <v>336</v>
       </c>
@@ -38533,7 +38725,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="337" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="12">
         <v>337</v>
       </c>
@@ -38616,7 +38808,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="338" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="12">
         <v>338</v>
       </c>
@@ -38699,7 +38891,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="339" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="12">
         <v>339</v>
       </c>
@@ -38782,7 +38974,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="340" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="12">
         <v>340</v>
       </c>
@@ -38865,7 +39057,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="341" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="12">
         <v>341</v>
       </c>
@@ -38948,7 +39140,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="342" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="12">
         <v>342</v>
       </c>
@@ -39031,7 +39223,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="343" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="12">
         <v>343</v>
       </c>
@@ -39114,7 +39306,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="344" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="12">
         <v>344</v>
       </c>
@@ -39197,7 +39389,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="345" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="12">
         <v>345</v>
       </c>
@@ -39280,7 +39472,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="346" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="12">
         <v>346</v>
       </c>
@@ -39363,7 +39555,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="347" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="12">
         <v>347</v>
       </c>
@@ -39446,7 +39638,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="348" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="12">
         <v>348</v>
       </c>
@@ -39529,7 +39721,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="349" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="12">
         <v>349</v>
       </c>
@@ -39612,7 +39804,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="350" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="12">
         <v>350</v>
       </c>
@@ -39695,7 +39887,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="351" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="12">
         <v>351</v>
       </c>
@@ -39778,7 +39970,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="352" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="12">
         <v>352</v>
       </c>
@@ -39861,7 +40053,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="353" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="12">
         <v>353</v>
       </c>
@@ -39944,7 +40136,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="354" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="12">
         <v>354</v>
       </c>
@@ -40027,7 +40219,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="355" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="12">
         <v>355</v>
       </c>
@@ -40110,7 +40302,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="356" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="12">
         <v>356</v>
       </c>
@@ -40193,7 +40385,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="357" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="12">
         <v>357</v>
       </c>
@@ -40276,7 +40468,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="358" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="12">
         <v>358</v>
       </c>
@@ -40359,7 +40551,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="359" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="12">
         <v>359</v>
       </c>
@@ -40442,7 +40634,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="360" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="12">
         <v>360</v>
       </c>
@@ -40525,7 +40717,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="361" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="12">
         <v>361</v>
       </c>
@@ -40608,7 +40800,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="362" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="12">
         <v>362</v>
       </c>
@@ -40691,7 +40883,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="363" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="12">
         <v>363</v>
       </c>
@@ -40774,7 +40966,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="364" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="12">
         <v>364</v>
       </c>
@@ -40857,7 +41049,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="365" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="12">
         <v>365</v>
       </c>
@@ -40940,7 +41132,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="366" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="12">
         <v>366</v>
       </c>
@@ -41023,7 +41215,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="367" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="12">
         <v>367</v>
       </c>
@@ -41106,7 +41298,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="368" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="12">
         <v>368</v>
       </c>
@@ -41189,7 +41381,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="369" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="12">
         <v>369</v>
       </c>
@@ -41272,7 +41464,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="370" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="12">
         <v>370</v>
       </c>
@@ -41355,7 +41547,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="371" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="12">
         <v>371</v>
       </c>
@@ -41438,7 +41630,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="372" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="12">
         <v>372</v>
       </c>
@@ -41521,7 +41713,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="373" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="12">
         <v>373</v>
       </c>
@@ -41604,7 +41796,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="374" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="12">
         <v>374</v>
       </c>
@@ -41687,7 +41879,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="375" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="12">
         <v>375</v>
       </c>
@@ -41770,7 +41962,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="376" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="12">
         <v>376</v>
       </c>
@@ -41853,7 +42045,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="377" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="12">
         <v>377</v>
       </c>
@@ -41936,7 +42128,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="378" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="12">
         <v>378</v>
       </c>
@@ -42019,7 +42211,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="379" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="12">
         <v>379</v>
       </c>
@@ -42102,7 +42294,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="380" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="12">
         <v>380</v>
       </c>
@@ -42185,7 +42377,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="381" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="12">
         <v>381</v>
       </c>
@@ -42268,7 +42460,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="382" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="12">
         <v>382</v>
       </c>
@@ -42351,7 +42543,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="383" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="12">
         <v>383</v>
       </c>
@@ -42434,7 +42626,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="384" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="12">
         <v>384</v>
       </c>
@@ -42517,7 +42709,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="385" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="12">
         <v>385</v>
       </c>
@@ -42600,7 +42792,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="386" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="12">
         <v>386</v>
       </c>
@@ -42683,7 +42875,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="387" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="12">
         <v>387</v>
       </c>
@@ -42766,7 +42958,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="388" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="12">
         <v>388</v>
       </c>
@@ -42849,7 +43041,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="389" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="12">
         <v>389</v>
       </c>
@@ -42932,7 +43124,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="390" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="12">
         <v>390</v>
       </c>
@@ -43015,7 +43207,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="391" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="12">
         <v>391</v>
       </c>
@@ -43098,7 +43290,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="392" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="12">
         <v>392</v>
       </c>
@@ -43181,7 +43373,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="393" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="12">
         <v>393</v>
       </c>
@@ -43264,7 +43456,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="394" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="12">
         <v>394</v>
       </c>
@@ -43347,7 +43539,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="395" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="12">
         <v>395</v>
       </c>
@@ -43430,7 +43622,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="396" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="12">
         <v>396</v>
       </c>
@@ -43513,7 +43705,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="397" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="12">
         <v>397</v>
       </c>
@@ -43596,7 +43788,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="398" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="12">
         <v>398</v>
       </c>
@@ -43679,7 +43871,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="399" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="12">
         <v>399</v>
       </c>
@@ -43762,7 +43954,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="400" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="12">
         <v>400</v>
       </c>
@@ -43845,7 +44037,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="401" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="12">
         <v>401</v>
       </c>
@@ -43928,7 +44120,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="402" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="12">
         <v>402</v>
       </c>
@@ -44011,7 +44203,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="403" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="12">
         <v>403</v>
       </c>
@@ -44094,7 +44286,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="404" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="12">
         <v>404</v>
       </c>
@@ -44177,7 +44369,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="405" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="12">
         <v>405</v>
       </c>
@@ -44260,7 +44452,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="406" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="12">
         <v>406</v>
       </c>
@@ -44343,7 +44535,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="407" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="12">
         <v>407</v>
       </c>
@@ -44426,7 +44618,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="408" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="12">
         <v>408</v>
       </c>
@@ -44509,7 +44701,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="409" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="12">
         <v>409</v>
       </c>
@@ -44592,7 +44784,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="410" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="12">
         <v>410</v>
       </c>
@@ -44675,7 +44867,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="411" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="12">
         <v>411</v>
       </c>
@@ -44758,7 +44950,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="412" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="12">
         <v>412</v>
       </c>
@@ -44841,7 +45033,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="413" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="12">
         <v>413</v>
       </c>
@@ -44924,7 +45116,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="414" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="12">
         <v>414</v>
       </c>
@@ -45007,7 +45199,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="415" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="12">
         <v>415</v>
       </c>
@@ -45090,7 +45282,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="416" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="12">
         <v>416</v>
       </c>
@@ -45173,7 +45365,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="417" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="12">
         <v>417</v>
       </c>
@@ -45256,7 +45448,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="418" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="12">
         <v>418</v>
       </c>
@@ -45339,7 +45531,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="419" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="12">
         <v>419</v>
       </c>
@@ -45422,7 +45614,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="420" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="12">
         <v>420</v>
       </c>
@@ -45505,7 +45697,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="421" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="12">
         <v>421</v>
       </c>
@@ -45588,7 +45780,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="422" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="12">
         <v>422</v>
       </c>
@@ -45671,7 +45863,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="423" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="12">
         <v>423</v>
       </c>
@@ -45754,7 +45946,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="424" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="12">
         <v>424</v>
       </c>
@@ -45837,7 +46029,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="425" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="12">
         <v>425</v>
       </c>
@@ -45920,7 +46112,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="426" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="12">
         <v>426</v>
       </c>
@@ -46003,7 +46195,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="427" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="12">
         <v>427</v>
       </c>
@@ -46086,7 +46278,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="428" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="12">
         <v>428</v>
       </c>
@@ -46169,7 +46361,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="429" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="12">
         <v>429</v>
       </c>
@@ -46252,7 +46444,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="430" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="12">
         <v>430</v>
       </c>
@@ -46335,7 +46527,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="431" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="12">
         <v>431</v>
       </c>
@@ -46418,7 +46610,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="432" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="12">
         <v>432</v>
       </c>
@@ -46501,7 +46693,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="433" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="12">
         <v>433</v>
       </c>
@@ -46584,7 +46776,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="434" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="12">
         <v>434</v>
       </c>
@@ -46667,7 +46859,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="435" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="12">
         <v>435</v>
       </c>
@@ -46750,7 +46942,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="436" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="12">
         <v>436</v>
       </c>
@@ -46833,7 +47025,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="437" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="12">
         <v>437</v>
       </c>
@@ -46916,7 +47108,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="438" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="12">
         <v>438</v>
       </c>
@@ -46999,7 +47191,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="439" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="12">
         <v>439</v>
       </c>
@@ -47082,7 +47274,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="440" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="12">
         <v>440</v>
       </c>
@@ -47165,7 +47357,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="441" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="12">
         <v>441</v>
       </c>
@@ -47248,7 +47440,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="442" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="12">
         <v>442</v>
       </c>
@@ -47331,7 +47523,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="443" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="12">
         <v>443</v>
       </c>
@@ -47414,7 +47606,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="444" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="12">
         <v>444</v>
       </c>
@@ -47497,7 +47689,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="445" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="12">
         <v>445</v>
       </c>
@@ -47580,7 +47772,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="446" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="12">
         <v>446</v>
       </c>
@@ -47663,7 +47855,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="447" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="12">
         <v>447</v>
       </c>
@@ -47746,7 +47938,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="448" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="12">
         <v>448</v>
       </c>
@@ -47829,7 +48021,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="449" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="12">
         <v>449</v>
       </c>
@@ -47912,7 +48104,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="450" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="12">
         <v>450</v>
       </c>
@@ -47995,7 +48187,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="451" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="12">
         <v>451</v>
       </c>
@@ -48078,7 +48270,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="452" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="12">
         <v>452</v>
       </c>
@@ -48161,7 +48353,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="453" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="12">
         <v>453</v>
       </c>
@@ -48244,7 +48436,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="454" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="12">
         <v>454</v>
       </c>
@@ -48327,7 +48519,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="455" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="12">
         <v>455</v>
       </c>
@@ -48410,7 +48602,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="456" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="12">
         <v>456</v>
       </c>
@@ -48493,7 +48685,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="457" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="12">
         <v>457</v>
       </c>
@@ -48576,7 +48768,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="458" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="12">
         <v>458</v>
       </c>
@@ -48659,7 +48851,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="459" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="12">
         <v>459</v>
       </c>
@@ -48742,7 +48934,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="460" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="12">
         <v>460</v>
       </c>
@@ -48825,7 +49017,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="461" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="12">
         <v>461</v>
       </c>
@@ -48908,7 +49100,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="462" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="12">
         <v>462</v>
       </c>
@@ -48991,7 +49183,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="463" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="12">
         <v>463</v>
       </c>
@@ -49074,7 +49266,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="464" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="12">
         <v>464</v>
       </c>
@@ -49157,7 +49349,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="465" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="12">
         <v>465</v>
       </c>
@@ -49240,7 +49432,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="466" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="12">
         <v>466</v>
       </c>
@@ -49323,7 +49515,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="467" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="12">
         <v>467</v>
       </c>
@@ -49406,7 +49598,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="468" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="12">
         <v>468</v>
       </c>
@@ -49489,7 +49681,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="469" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="12">
         <v>469</v>
       </c>
@@ -49572,7 +49764,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="470" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="12">
         <v>470</v>
       </c>
@@ -49655,7 +49847,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="471" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="12">
         <v>471</v>
       </c>
@@ -49738,7 +49930,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="472" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="12">
         <v>472</v>
       </c>
@@ -49821,7 +50013,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="473" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="12">
         <v>473</v>
       </c>
@@ -49904,7 +50096,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="474" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="12">
         <v>474</v>
       </c>
@@ -49987,7 +50179,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="475" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="12">
         <v>475</v>
       </c>
@@ -50070,7 +50262,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="476" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="12">
         <v>476</v>
       </c>
@@ -50153,7 +50345,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="477" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="12">
         <v>477</v>
       </c>
@@ -50236,7 +50428,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="478" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="12">
         <v>478</v>
       </c>
@@ -50319,7 +50511,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="479" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="12">
         <v>479</v>
       </c>
@@ -50402,7 +50594,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="480" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="12">
         <v>480</v>
       </c>
@@ -50485,7 +50677,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="481" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="12">
         <v>481</v>
       </c>
@@ -50568,7 +50760,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="482" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="12">
         <v>482</v>
       </c>
@@ -50651,7 +50843,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="483" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="12">
         <v>483</v>
       </c>
@@ -50734,7 +50926,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="484" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="12">
         <v>484</v>
       </c>
@@ -50817,7 +51009,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="485" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="12">
         <v>485</v>
       </c>
@@ -50900,7 +51092,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="486" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="12">
         <v>486</v>
       </c>
@@ -50983,7 +51175,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="487" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="12">
         <v>487</v>
       </c>
@@ -51066,7 +51258,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="488" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="12">
         <v>488</v>
       </c>
@@ -51149,7 +51341,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="489" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="12">
         <v>489</v>
       </c>
@@ -51232,7 +51424,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="490" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="12">
         <v>490</v>
       </c>
@@ -51315,7 +51507,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="491" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="12">
         <v>491</v>
       </c>
@@ -51398,7 +51590,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="492" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="12">
         <v>492</v>
       </c>
@@ -51481,7 +51673,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="493" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="12">
         <v>493</v>
       </c>
@@ -51564,7 +51756,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="494" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="12">
         <v>494</v>
       </c>
@@ -51647,7 +51839,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="495" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="12">
         <v>495</v>
       </c>
@@ -51730,7 +51922,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="496" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="12">
         <v>496</v>
       </c>
@@ -51813,7 +52005,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="497" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="12">
         <v>497</v>
       </c>
@@ -51896,7 +52088,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="498" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="12">
         <v>498</v>
       </c>
@@ -51979,7 +52171,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="499" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="12">
         <v>499</v>
       </c>
@@ -52062,7 +52254,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="500" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="12">
         <v>500</v>
       </c>
@@ -52145,7 +52337,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="501" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="12">
         <v>501</v>
       </c>
@@ -52228,7 +52420,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="502" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="12">
         <v>502</v>
       </c>
@@ -52311,7 +52503,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="503" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="12">
         <v>503</v>
       </c>
@@ -52394,7 +52586,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="504" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="12">
         <v>504</v>
       </c>
@@ -52477,7 +52669,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="505" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="12">
         <v>505</v>
       </c>
@@ -52560,7 +52752,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="506" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="12">
         <v>506</v>
       </c>
@@ -52643,7 +52835,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="507" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="12">
         <v>507</v>
       </c>
@@ -52726,7 +52918,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="508" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="12">
         <v>508</v>
       </c>
@@ -52809,7 +53001,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="509" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="12">
         <v>509</v>
       </c>
@@ -52892,7 +53084,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="510" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="12">
         <v>510</v>
       </c>
@@ -52975,7 +53167,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="511" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="12">
         <v>511</v>
       </c>
@@ -53058,7 +53250,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="512" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="12">
         <v>512</v>
       </c>
@@ -53141,7 +53333,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="513" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="12">
         <v>513</v>
       </c>
@@ -53224,7 +53416,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="514" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="12">
         <v>514</v>
       </c>
@@ -53307,7 +53499,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="515" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="12">
         <v>515</v>
       </c>
@@ -53390,7 +53582,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="516" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="12">
         <v>516</v>
       </c>
@@ -53473,7 +53665,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="517" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="12">
         <v>517</v>
       </c>
@@ -53556,7 +53748,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="518" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="12">
         <v>518</v>
       </c>
@@ -53639,7 +53831,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="519" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="12">
         <v>519</v>
       </c>
@@ -53722,7 +53914,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="520" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="12">
         <v>520</v>
       </c>
@@ -53805,7 +53997,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="521" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="12">
         <v>521</v>
       </c>
@@ -53888,7 +54080,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="522" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="12">
         <v>522</v>
       </c>
@@ -53971,7 +54163,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="523" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="12">
         <v>523</v>
       </c>
@@ -54054,7 +54246,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="524" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="12">
         <v>524</v>
       </c>
@@ -54137,7 +54329,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="525" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="12">
         <v>525</v>
       </c>
@@ -54220,7 +54412,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="526" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="12">
         <v>526</v>
       </c>
@@ -54303,7 +54495,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="527" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="12">
         <v>527</v>
       </c>
@@ -54386,7 +54578,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="528" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="12">
         <v>528</v>
       </c>
@@ -54469,7 +54661,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="529" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="12">
         <v>529</v>
       </c>
@@ -54552,7 +54744,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="530" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="12">
         <v>530</v>
       </c>
@@ -54635,7 +54827,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="531" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="12">
         <v>531</v>
       </c>
@@ -54718,7 +54910,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="532" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="12">
         <v>532</v>
       </c>
@@ -54801,7 +54993,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="533" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="12">
         <v>533</v>
       </c>
@@ -54884,7 +55076,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="534" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="12">
         <v>534</v>
       </c>
@@ -54967,7 +55159,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="535" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="12">
         <v>535</v>
       </c>
@@ -55050,7 +55242,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="536" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="12">
         <v>536</v>
       </c>
@@ -55133,7 +55325,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="537" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="12">
         <v>537</v>
       </c>
@@ -55216,7 +55408,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="538" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="12">
         <v>538</v>
       </c>
@@ -55299,7 +55491,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="539" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="12">
         <v>539</v>
       </c>
@@ -55382,7 +55574,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="540" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="12">
         <v>540</v>
       </c>
@@ -55465,7 +55657,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="541" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="12">
         <v>541</v>
       </c>
@@ -55548,7 +55740,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="542" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="12">
         <v>542</v>
       </c>
@@ -55631,7 +55823,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="543" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="12">
         <v>543</v>
       </c>
@@ -55714,7 +55906,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="544" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="12">
         <v>544</v>
       </c>
@@ -55797,7 +55989,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="545" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="12">
         <v>545</v>
       </c>
@@ -55880,7 +56072,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="546" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="12">
         <v>546</v>
       </c>
@@ -55963,7 +56155,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="547" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="12">
         <v>547</v>
       </c>
@@ -56046,7 +56238,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="548" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="12">
         <v>548</v>
       </c>
@@ -56129,7 +56321,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="549" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="12">
         <v>549</v>
       </c>
@@ -56212,7 +56404,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="550" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="12">
         <v>550</v>
       </c>
@@ -56295,7 +56487,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="551" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="12">
         <v>551</v>
       </c>
@@ -56378,7 +56570,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="552" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="12">
         <v>552</v>
       </c>
@@ -56461,7 +56653,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="553" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="12">
         <v>553</v>
       </c>
@@ -56544,7 +56736,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="554" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="12">
         <v>554</v>
       </c>
@@ -56627,7 +56819,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="555" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="12">
         <v>555</v>
       </c>
@@ -56710,7 +56902,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="556" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="12">
         <v>556</v>
       </c>
@@ -56793,7 +56985,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="557" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="12">
         <v>557</v>
       </c>
@@ -56876,7 +57068,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="558" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="12">
         <v>558</v>
       </c>
@@ -56959,7 +57151,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="559" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="12">
         <v>559</v>
       </c>
@@ -57042,7 +57234,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="560" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="12">
         <v>560</v>
       </c>
@@ -57125,7 +57317,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="561" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="12">
         <v>561</v>
       </c>
@@ -57208,7 +57400,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="562" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="12">
         <v>562</v>
       </c>
@@ -57291,7 +57483,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="563" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="12">
         <v>563</v>
       </c>
@@ -57374,7 +57566,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="564" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="12">
         <v>564</v>
       </c>
@@ -57457,7 +57649,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="565" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="12">
         <v>565</v>
       </c>
@@ -57540,7 +57732,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="566" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="12">
         <v>566</v>
       </c>
@@ -57623,7 +57815,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="567" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="12">
         <v>567</v>
       </c>
@@ -57706,7 +57898,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="568" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="12">
         <v>568</v>
       </c>
@@ -57789,7 +57981,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="569" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="12">
         <v>569</v>
       </c>
@@ -57872,7 +58064,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="570" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="12">
         <v>570</v>
       </c>
@@ -57955,7 +58147,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="571" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="12">
         <v>571</v>
       </c>
@@ -58038,7 +58230,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="572" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="12">
         <v>572</v>
       </c>
@@ -58121,7 +58313,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="573" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="12">
         <v>573</v>
       </c>
@@ -58204,7 +58396,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="574" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="12">
         <v>574</v>
       </c>
@@ -58287,7 +58479,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="575" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="12">
         <v>575</v>
       </c>
@@ -58370,7 +58562,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="576" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="12">
         <v>576</v>
       </c>
@@ -58453,7 +58645,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="577" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="12">
         <v>577</v>
       </c>
@@ -58536,7 +58728,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="578" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="12">
         <v>578</v>
       </c>
@@ -58619,7 +58811,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="579" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="12">
         <v>579</v>
       </c>
@@ -58702,7 +58894,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="580" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="12">
         <v>580</v>
       </c>
@@ -58785,7 +58977,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="581" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="12">
         <v>581</v>
       </c>
@@ -58868,7 +59060,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="582" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="12">
         <v>582</v>
       </c>
@@ -58951,7 +59143,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="583" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="12">
         <v>583</v>
       </c>
@@ -59034,7 +59226,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="584" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="12">
         <v>584</v>
       </c>
@@ -59117,7 +59309,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="585" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="12">
         <v>585</v>
       </c>
@@ -59200,7 +59392,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="586" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="12">
         <v>586</v>
       </c>
@@ -59283,7 +59475,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="587" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="12">
         <v>587</v>
       </c>
@@ -59366,7 +59558,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="588" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="12">
         <v>588</v>
       </c>
@@ -59449,7 +59641,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="589" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="12">
         <v>589</v>
       </c>
@@ -59532,7 +59724,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="590" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="12">
         <v>590</v>
       </c>
@@ -59615,7 +59807,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="591" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="12">
         <v>591</v>
       </c>
@@ -59698,7 +59890,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="592" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="12">
         <v>592</v>
       </c>
@@ -59781,7 +59973,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="593" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="12">
         <v>593</v>
       </c>
@@ -59864,7 +60056,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="594" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="12">
         <v>594</v>
       </c>
@@ -59947,7 +60139,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="595" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="12">
         <v>595</v>
       </c>
@@ -60030,7 +60222,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="596" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="12">
         <v>596</v>
       </c>
@@ -60113,7 +60305,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="597" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="12">
         <v>597</v>
       </c>
@@ -60196,7 +60388,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="598" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="12">
         <v>598</v>
       </c>
@@ -60279,7 +60471,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="599" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="12">
         <v>599</v>
       </c>
@@ -60362,7 +60554,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="600" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="12">
         <v>600</v>
       </c>
@@ -60445,7 +60637,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="601" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="12">
         <v>601</v>
       </c>
@@ -60528,7 +60720,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="602" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="12">
         <v>602</v>
       </c>
@@ -60611,7 +60803,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="603" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="12">
         <v>603</v>
       </c>
@@ -60694,7 +60886,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="604" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="12">
         <v>604</v>
       </c>
@@ -60777,7 +60969,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="605" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="12">
         <v>605</v>
       </c>
@@ -60860,7 +61052,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="606" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="12">
         <v>606</v>
       </c>
@@ -60943,7 +61135,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="607" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="12">
         <v>607</v>
       </c>
@@ -61026,7 +61218,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="608" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="12">
         <v>608</v>
       </c>
@@ -61109,7 +61301,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="609" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="12">
         <v>609</v>
       </c>
@@ -61192,7 +61384,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="610" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="12">
         <v>610</v>
       </c>
@@ -61275,7 +61467,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="611" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="12">
         <v>611</v>
       </c>
@@ -61358,7 +61550,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="612" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="12">
         <v>612</v>
       </c>
@@ -61441,7 +61633,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="613" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="12">
         <v>613</v>
       </c>
@@ -61524,7 +61716,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="614" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="12">
         <v>614</v>
       </c>
@@ -61607,7 +61799,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="615" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="12">
         <v>615</v>
       </c>
@@ -61690,7 +61882,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="616" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="12">
         <v>616</v>
       </c>
@@ -61773,7 +61965,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="617" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="12">
         <v>617</v>
       </c>
@@ -61856,7 +62048,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="618" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="12">
         <v>618</v>
       </c>
@@ -61939,7 +62131,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="619" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="12">
         <v>619</v>
       </c>
@@ -62022,7 +62214,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="620" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="12">
         <v>620</v>
       </c>
@@ -62105,7 +62297,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="621" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="12">
         <v>621</v>
       </c>
@@ -62188,7 +62380,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="622" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="12">
         <v>622</v>
       </c>
@@ -62271,7 +62463,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="623" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="12">
         <v>623</v>
       </c>
@@ -62354,7 +62546,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="624" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="12">
         <v>624</v>
       </c>
@@ -62437,7 +62629,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="625" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="12">
         <v>625</v>
       </c>
@@ -62520,7 +62712,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="626" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="12">
         <v>626</v>
       </c>
@@ -62603,7 +62795,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="627" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="12">
         <v>627</v>
       </c>
@@ -62686,7 +62878,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="628" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="12">
         <v>628</v>
       </c>
@@ -62769,7 +62961,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="629" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="12">
         <v>629</v>
       </c>
@@ -62852,7 +63044,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="630" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="12">
         <v>630</v>
       </c>
@@ -62935,7 +63127,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="631" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="12">
         <v>631</v>
       </c>
@@ -63018,7 +63210,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="632" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="12">
         <v>632</v>
       </c>
@@ -63101,7 +63293,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="633" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="12">
         <v>633</v>
       </c>
@@ -63184,7 +63376,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="634" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="12">
         <v>634</v>
       </c>
@@ -63267,7 +63459,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="635" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="12">
         <v>635</v>
       </c>
@@ -63350,7 +63542,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="636" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="12">
         <v>636</v>
       </c>
@@ -63433,7 +63625,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="637" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="12">
         <v>637</v>
       </c>
@@ -63516,7 +63708,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="638" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="12">
         <v>638</v>
       </c>
@@ -63599,7 +63791,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="639" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="12">
         <v>639</v>
       </c>
@@ -63682,7 +63874,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="640" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="12">
         <v>640</v>
       </c>
@@ -63765,7 +63957,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="641" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="12">
         <v>641</v>
       </c>
@@ -63848,7 +64040,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="642" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="12">
         <v>642</v>
       </c>
@@ -63931,7 +64123,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="643" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="12">
         <v>643</v>
       </c>
@@ -64014,7 +64206,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="644" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="12">
         <v>644</v>
       </c>
@@ -64097,7 +64289,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="645" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="12">
         <v>645</v>
       </c>
@@ -64180,7 +64372,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="646" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="12">
         <v>646</v>
       </c>
@@ -64263,7 +64455,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="647" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="12">
         <v>647</v>
       </c>
@@ -64346,7 +64538,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="648" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="12">
         <v>648</v>
       </c>
@@ -64429,7 +64621,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="649" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="12">
         <v>649</v>
       </c>
@@ -64512,7 +64704,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="650" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="12">
         <v>650</v>
       </c>
@@ -64595,7 +64787,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="651" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="12">
         <v>651</v>
       </c>
@@ -64678,7 +64870,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="652" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="12">
         <v>652</v>
       </c>
@@ -64761,7 +64953,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="653" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="12">
         <v>653</v>
       </c>
@@ -64844,7 +65036,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="654" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="12">
         <v>654</v>
       </c>
@@ -64927,7 +65119,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="655" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="12">
         <v>655</v>
       </c>
@@ -65010,7 +65202,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="656" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="12">
         <v>656</v>
       </c>
@@ -65093,7 +65285,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="657" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="12">
         <v>657</v>
       </c>
@@ -65176,7 +65368,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="658" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="12">
         <v>658</v>
       </c>
@@ -65259,7 +65451,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="659" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="12">
         <v>659</v>
       </c>
@@ -65342,7 +65534,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="660" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="12">
         <v>660</v>
       </c>
@@ -65425,7 +65617,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="661" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="12">
         <v>661</v>
       </c>
@@ -65508,7 +65700,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="662" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="12">
         <v>662</v>
       </c>
@@ -65591,7 +65783,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="663" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="12">
         <v>663</v>
       </c>
@@ -65674,7 +65866,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="664" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="12">
         <v>664</v>
       </c>
@@ -65757,7 +65949,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="665" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="12">
         <v>665</v>
       </c>
@@ -65840,7 +66032,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="666" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="12">
         <v>666</v>
       </c>
@@ -65923,7 +66115,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="667" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="12">
         <v>667</v>
       </c>
@@ -66006,7 +66198,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="668" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="12">
         <v>668</v>
       </c>
@@ -66089,7 +66281,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="669" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="12">
         <v>669</v>
       </c>
@@ -66172,7 +66364,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="670" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="12">
         <v>670</v>
       </c>
@@ -66255,7 +66447,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="671" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="12">
         <v>671</v>
       </c>
@@ -66338,7 +66530,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="672" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="12">
         <v>672</v>
       </c>
@@ -66421,7 +66613,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="673" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="12">
         <v>673</v>
       </c>
@@ -66504,7 +66696,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="674" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="12">
         <v>674</v>
       </c>
@@ -66587,7 +66779,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="675" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="12">
         <v>675</v>
       </c>
@@ -66670,7 +66862,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="676" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="12">
         <v>676</v>
       </c>
@@ -66753,7 +66945,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="677" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="12">
         <v>677</v>
       </c>
@@ -66836,7 +67028,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="678" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="12">
         <v>678</v>
       </c>
@@ -66919,7 +67111,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="679" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="12">
         <v>679</v>
       </c>
@@ -67002,7 +67194,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="680" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="12">
         <v>680</v>
       </c>
@@ -67085,7 +67277,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="681" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="12">
         <v>681</v>
       </c>
@@ -67168,7 +67360,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="682" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="12">
         <v>682</v>
       </c>
@@ -67251,7 +67443,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="683" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="12">
         <v>683</v>
       </c>
@@ -67334,7 +67526,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="684" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="12">
         <v>684</v>
       </c>
@@ -67417,7 +67609,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="685" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="12">
         <v>685</v>
       </c>
@@ -67500,7 +67692,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="686" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="12">
         <v>686</v>
       </c>
@@ -67583,7 +67775,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="687" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="12">
         <v>687</v>
       </c>
@@ -67666,7 +67858,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="688" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="12">
         <v>688</v>
       </c>
@@ -67749,7 +67941,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="689" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="12">
         <v>689</v>
       </c>
@@ -67832,7 +68024,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="690" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="12">
         <v>690</v>
       </c>
@@ -67915,7 +68107,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="691" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="12">
         <v>691</v>
       </c>
@@ -67998,7 +68190,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="692" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="12">
         <v>692</v>
       </c>
@@ -68081,7 +68273,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="693" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="12">
         <v>693</v>
       </c>
@@ -68164,7 +68356,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="694" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="12">
         <v>694</v>
       </c>
@@ -68247,7 +68439,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="695" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="12">
         <v>695</v>
       </c>
@@ -68330,7 +68522,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="696" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="12">
         <v>696</v>
       </c>
@@ -68413,7 +68605,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="697" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="12">
         <v>697</v>
       </c>
@@ -68496,7 +68688,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="698" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="12">
         <v>698</v>
       </c>
@@ -68579,7 +68771,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="699" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="12">
         <v>699</v>
       </c>
@@ -68662,7 +68854,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="700" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="12">
         <v>700</v>
       </c>
@@ -68745,7 +68937,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="701" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="12">
         <v>701</v>
       </c>
@@ -68828,7 +69020,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="702" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="12">
         <v>702</v>
       </c>
@@ -68911,7 +69103,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="703" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="12">
         <v>703</v>
       </c>
@@ -68994,7 +69186,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="704" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="12">
         <v>704</v>
       </c>
@@ -69077,7 +69269,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="705" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="12">
         <v>705</v>
       </c>
@@ -69160,7 +69352,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="706" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="12">
         <v>706</v>
       </c>
@@ -69243,7 +69435,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="707" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="12">
         <v>707</v>
       </c>
@@ -69326,7 +69518,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="708" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="12">
         <v>708</v>
       </c>
@@ -69409,7 +69601,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="709" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="12">
         <v>709</v>
       </c>
@@ -69492,7 +69684,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="710" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="12">
         <v>710</v>
       </c>
@@ -69575,7 +69767,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="711" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="12">
         <v>711</v>
       </c>
@@ -69658,7 +69850,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="712" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="12">
         <v>712</v>
       </c>
@@ -69741,7 +69933,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="713" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="12">
         <v>713</v>
       </c>
@@ -69824,7 +70016,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="714" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="12">
         <v>714</v>
       </c>
@@ -69907,7 +70099,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="715" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="12">
         <v>715</v>
       </c>
@@ -69990,7 +70182,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="716" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="12">
         <v>716</v>
       </c>
@@ -70073,7 +70265,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="717" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="12">
         <v>717</v>
       </c>
@@ -70156,7 +70348,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="718" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="12">
         <v>718</v>
       </c>
@@ -70239,7 +70431,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="719" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="12">
         <v>719</v>
       </c>
@@ -70322,7 +70514,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="720" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="12">
         <v>720</v>
       </c>
@@ -70405,7 +70597,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="721" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="12">
         <v>721</v>
       </c>
@@ -70488,7 +70680,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="722" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="12">
         <v>722</v>
       </c>
@@ -70571,7 +70763,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="723" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="12">
         <v>723</v>
       </c>
@@ -70654,7 +70846,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="724" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="12">
         <v>724</v>
       </c>
@@ -70737,7 +70929,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="725" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="12">
         <v>725</v>
       </c>
@@ -70820,7 +71012,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="726" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="12">
         <v>726</v>
       </c>
@@ -70903,7 +71095,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="727" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="12">
         <v>727</v>
       </c>
@@ -70986,7 +71178,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="728" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="12">
         <v>728</v>
       </c>
@@ -71069,7 +71261,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="729" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A729" s="12">
         <v>729</v>
       </c>
@@ -71152,7 +71344,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="730" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="12">
         <v>730</v>
       </c>
@@ -71235,7 +71427,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="731" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="12">
         <v>731</v>
       </c>
@@ -71318,7 +71510,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="732" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="12">
         <v>732</v>
       </c>
@@ -71407,65 +71599,65 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:I2 N2:Q2 AB2:XFD2 P2:AA732 D3:E3 D4:D732">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 F1">
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="10" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="9" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
